--- a/resultados/apucarana/erros_varredura.xlsx
+++ b/resultados/apucarana/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,6 +504,7062 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>http://apucarana.pr.gov.br/pss/inscricao</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>404</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:02:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>http://sys.apucarana.pr.gov.br/apucarana-pr/uploads/madspot_1433631749.php</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>404</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/site/carta-de-servicos/programa-portas-abertas-cursos-profissionalizantes/</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>404</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:06:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://compra.apucarana.pr.gov.br/services/strategy-planning/</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>404</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:11:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://compra.apucarana.pr.gov.br/services/audit-evaluation/</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>404</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:11:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://compra.apucarana.pr.gov.br/services/insurance/</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>404</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:11:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://compra.apucarana.pr.gov.br/services/financial-services/</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>404</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:12:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://compra.apucarana.pr.gov.br/services/communications/</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>404</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:12:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://compra.apucarana.pr.gov.br/services/consumer-markets/</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>404</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:12:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>404</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:15:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>404</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:15:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/certidao-negativa-de-debitos</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>404</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:15:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/certidao-negativa-de-debitos/detalhar/1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>404</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-issalvara</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>404</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:15:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-issalvara/detalhar/1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>404</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:15:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-iptu</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>404</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:16:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-iptu/detalhar/1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>404</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:16:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/site/servicos/nfs-e/Imh0dHBzOlwvXC9uZnNlLWFwdWNhcmFuYS5hdGVuZGUubmV0XC9hdXRvYXRlbmRpbWVudG9cLyI=</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>404</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:16:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/consulta-de-licitacoes</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>404</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:16:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/consulta-de-licitacoes/detalhar/1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>404</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:16:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/@licitacaoapucarana6363/videos?view=0&amp;sort=dd&amp;shelf_id=1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>404</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:16:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/watch?v=gruiYX3DvAo</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>404</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:16:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/sitemap</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>404</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:16:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Institucional/MISSAO-VISAO-DE-FUTURO-VALORES</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>404</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:17:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Institucional/QUEM-SOMOS-E-O-QUE-FAZEMOS</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>404</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:17:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Institucional/DIRETORIA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>404</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:17:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Pagina/estatuto_social</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>404</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:17:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Pagina/GOVERNANCA-CORPORATIVA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>404</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:17:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Institucional/ATIVIDADES-DE-GESTAO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>404</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:17:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Institucional/GESTAO-DE-RISCOS-E-GERENCIAMENTO-DE-CAPITAL</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>404</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:17:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Pagina/POLITICA-DE-RESPONSABILIDADE-SOCIOAMBIENTAL</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>404</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:17:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Microcredito-Facil</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>404</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:18:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Banco-da-Mulher-Paranaense/Microcredito</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>404</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:18:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Credito/Banco-da-Mulher-Paranaense/MPE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>404</v>
+      </c>
+      <c r="E37" t="n">
+        <v>4</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:18:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Credito/BANCO-DO-EMPREENDEDOR</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>404</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:18:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Emprestimos</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>404</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:18:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Credito/AMPLIACAO-CONSTRUCAO-E-REFORMA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>404</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:18:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Credito/MAQUINAS-E-EQUIPAMENTOS</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>404</v>
+      </c>
+      <c r="E41" t="n">
+        <v>4</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:18:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Credito/VEICULOS</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>404</v>
+      </c>
+      <c r="E42" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:18:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Credito/Energias-Renovaveis</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>404</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:18:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Credito/Fomento-Inova</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>404</v>
+      </c>
+      <c r="E44" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:19:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Credito/Recursos-BNDES</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>404</v>
+      </c>
+      <c r="E45" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:19:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Credito/FINANCIAMENTOS-AO-SETOR-PUBLICO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>404</v>
+      </c>
+      <c r="E46" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:19:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Transparencia/Tabela-de-Tarifas</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>404</v>
+      </c>
+      <c r="E47" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:19:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Pagina/CUSTO-EFETIVO-TOTAL-CET</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>404</v>
+      </c>
+      <c r="E48" t="n">
+        <v>4</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:19:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Parcerias/AGENDA-DE-CURSOS</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>404</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:19:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Parcerias/AGENTES-DE-CREDITO</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>404</v>
+      </c>
+      <c r="E50" t="n">
+        <v>4</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:19:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Parcerias/SEJA-UM-AGENTE-DE-CREDITO</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>404</v>
+      </c>
+      <c r="E51" t="n">
+        <v>4</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:19:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Pagina/NOSSOS-CORRESPONDENTES</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>404</v>
+      </c>
+      <c r="E52" t="n">
+        <v>4</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:20:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Pagina/CORRESPONDENTES</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>404</v>
+      </c>
+      <c r="E53" t="n">
+        <v>4</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:20:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Pagina/COMO-SE-TORNAR-CORRESPONDENTE</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>404</v>
+      </c>
+      <c r="E54" t="n">
+        <v>4</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:20:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Pagina/Transparencia</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>404</v>
+      </c>
+      <c r="E55" t="n">
+        <v>4</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:20:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Transparencia/CONCURSOS-PUBLICOS</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>404</v>
+      </c>
+      <c r="E56" t="n">
+        <v>4</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:20:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Transparencia/Editais</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>404</v>
+      </c>
+      <c r="E57" t="n">
+        <v>4</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:20:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Transparencia/DEMONSTRATIVOS-CONTABEIS-FOMENTO-PARANA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>404</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:20:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Fundos/DEMONSTRATIVOS-CONTABEIS-GESTAO-DE-FUNDOS</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>404</v>
+      </c>
+      <c r="E59" t="n">
+        <v>4</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:20:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/contatos</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>404</v>
+      </c>
+      <c r="E60" t="n">
+        <v>4</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:21:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-credito-para-micro-e-pequenas-empresas-JVN6AGoP</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>404</v>
+      </c>
+      <c r="E61" t="n">
+        <v>4</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:21:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-financiamento-ao-Banco-da-Mulher-Paranaense-aPo4dBom</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>404</v>
+      </c>
+      <c r="E62" t="n">
+        <v>4</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:21:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-microcredito-para-empreendedores-nQ3x0z32</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>404</v>
+      </c>
+      <c r="E63" t="n">
+        <v>4</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:21:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/servicos/Empresa/Cadin/Consultar-se-o-CPF-ou-o-CNPJ-esta-inscrito-no-Cadin-aPo4ZB3m</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>404</v>
+      </c>
+      <c r="E64" t="n">
+        <v>4</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:21:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/servicos/Mais-buscados/Certidoes/Emitir-Certidao-Negativa-Receita-Estadual-kZrX5gol</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>404</v>
+      </c>
+      <c r="E65" t="n">
+        <v>4</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:21:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/servicos/Seguranca/Atestados-e-Certidoes/Solicitar-Atestado-de-Cadastro-Negativo-vGr5V6o0</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>404</v>
+      </c>
+      <c r="E66" t="n">
+        <v>4</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:21:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/servicos/Servicos/Meio-Ambiente/Solicitar-licenciamento-ambiental-9OoqbNG0</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>404</v>
+      </c>
+      <c r="E67" t="n">
+        <v>4</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:21:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/servicos/Receita-PR/Acesso-ao-portal/Acessar-o-Portal-Receita-PR-ybrz8JN4</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>404</v>
+      </c>
+      <c r="E68" t="n">
+        <v>4</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:22:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/servicos/Administracao/Documentos/Cadastrar-se-no-PIA-6K3WwW3m</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>404</v>
+      </c>
+      <c r="E69" t="n">
+        <v>4</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:22:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/servicos/Seguranca/Corpo-de-Bombeiros/Solicitar-analise-de-projeto-pelo-Corpo-de-Bombeiros-0GNAZ387</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>404</v>
+      </c>
+      <c r="E70" t="n">
+        <v>4</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:22:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/servicos/Servicos/Municipios/Solicitar-financiamento-do-BRDE-kZrXMDol</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>404</v>
+      </c>
+      <c r="E71" t="n">
+        <v>4</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:22:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/servicos/Servicos/Licenciamento/Solicitar-licenciamento-do-Corpo-de-Bombeiros-MD3PPn36</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>404</v>
+      </c>
+      <c r="E72" t="n">
+        <v>4</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:22:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Pagina/Ouvidoria</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>404</v>
+      </c>
+      <c r="E73" t="n">
+        <v>4</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:22:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/apucarana/</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>404</v>
+      </c>
+      <c r="E74" t="n">
+        <v>4</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:22:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/o-que-fazer/</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>404</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:22:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/onde-comer/</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>404</v>
+      </c>
+      <c r="E76" t="n">
+        <v>4</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:22:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/onde-ficar/</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>404</v>
+      </c>
+      <c r="E77" t="n">
+        <v>4</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:23:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/eventos/</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>404</v>
+      </c>
+      <c r="E78" t="n">
+        <v>4</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:23:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/servicos/</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>404</v>
+      </c>
+      <c r="E79" t="n">
+        <v>4</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:23:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/ao-vivo/</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>404</v>
+      </c>
+      <c r="E80" t="n">
+        <v>4</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:23:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/travel-guide/conhecendo-apucarana</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>404</v>
+      </c>
+      <c r="E81" t="n">
+        <v>4</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:23:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/atrativos-da-serra/</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>404</v>
+      </c>
+      <c r="E82" t="n">
+        <v>4</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:23:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/noites-em-apucarana/</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>404</v>
+      </c>
+      <c r="E83" t="n">
+        <v>4</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:23:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/cafes-e-padarias/</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>404</v>
+      </c>
+      <c r="E84" t="n">
+        <v>4</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:23:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/natureza/</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>404</v>
+      </c>
+      <c r="E85" t="n">
+        <v>4</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:24:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/arte-cultura/</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>404</v>
+      </c>
+      <c r="E86" t="n">
+        <v>4</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:24:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/tour/catedral-nossa-senhora-de-lourdes/</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>404</v>
+      </c>
+      <c r="E87" t="n">
+        <v>4</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:24:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/tour/praca-rui-barbosa/</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>404</v>
+      </c>
+      <c r="E88" t="n">
+        <v>4</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:24:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/tour/parque-jaboti/</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>404</v>
+      </c>
+      <c r="E89" t="n">
+        <v>4</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:24:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/tour/espaco-das-feiras/</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>404</v>
+      </c>
+      <c r="E90" t="n">
+        <v>4</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:24:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/tour/parque-ecologico-da-raposa/</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>404</v>
+      </c>
+      <c r="E91" t="n">
+        <v>4</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:24:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/tour/praca-maua/</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>404</v>
+      </c>
+      <c r="E92" t="n">
+        <v>4</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:24:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/tour/parque-da-redencao/</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>404</v>
+      </c>
+      <c r="E93" t="n">
+        <v>4</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:25:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/tour/jardim-japones/</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>404</v>
+      </c>
+      <c r="E94" t="n">
+        <v>4</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:25:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/tour/praca-da-onca/</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>404</v>
+      </c>
+      <c r="E95" t="n">
+        <v>4</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:25:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/tour/bosque-municipal/</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>404</v>
+      </c>
+      <c r="E96" t="n">
+        <v>4</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:25:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/tour/museu-do-cafe/</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>404</v>
+      </c>
+      <c r="E97" t="n">
+        <v>4</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:25:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/tour/parque-ecologico-santo-expedito/</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>404</v>
+      </c>
+      <c r="E98" t="n">
+        <v>4</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:25:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/compre-roupas-direto-do-fabricante/</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>404</v>
+      </c>
+      <c r="E99" t="n">
+        <v>4</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:25:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/roteiro-da-fe/</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>404</v>
+      </c>
+      <c r="E100" t="n">
+        <v>4</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:25:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/roteiros-turisticos/</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>404</v>
+      </c>
+      <c r="E101" t="n">
+        <v>4</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:25:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/tour/monumento-a-biblia/</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>404</v>
+      </c>
+      <c r="E102" t="n">
+        <v>4</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:26:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/tour/monumento-ao-bone/</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>404</v>
+      </c>
+      <c r="E103" t="n">
+        <v>4</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:26:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/tour/centro-civico/</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>404</v>
+      </c>
+      <c r="E104" t="n">
+        <v>4</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:26:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/tour/memorial-casa-de-portugal-e-praca-jose-lebre-dos-santos/</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>404</v>
+      </c>
+      <c r="E105" t="n">
+        <v>4</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:26:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/tour/exposicao-iconografica-josefina-mariana-e-marelliana/</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>404</v>
+      </c>
+      <c r="E106" t="n">
+        <v>4</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:26:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/tour/praca-28-de-janeiro/</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>404</v>
+      </c>
+      <c r="E107" t="n">
+        <v>4</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:26:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/tour/parque-biguacu/</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>404</v>
+      </c>
+      <c r="E108" t="n">
+        <v>4</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:26:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/tour/museu-municipal-de-apucarana/</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>404</v>
+      </c>
+      <c r="E109" t="n">
+        <v>4</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:26:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/credenciamento/</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>404</v>
+      </c>
+      <c r="E110" t="n">
+        <v>4</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:27:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/multi.php</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>404</v>
+      </c>
+      <c r="E111" t="n">
+        <v>4</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:27:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/medica.php</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>404</v>
+      </c>
+      <c r="E112" t="n">
+        <v>4</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:27:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/editais.php</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>404</v>
+      </c>
+      <c r="E113" t="n">
+        <v>4</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:27:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/inscricoes.php</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>404</v>
+      </c>
+      <c r="E114" t="n">
+        <v>4</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:28:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/contato.php</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>404</v>
+      </c>
+      <c r="E115" t="n">
+        <v>4</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:28:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/e-obituarios</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>404</v>
+      </c>
+      <c r="E116" t="n">
+        <v>4</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:28:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/e-obituarios/detalhar/1</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>404</v>
+      </c>
+      <c r="E117" t="n">
+        <v>4</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:28:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>https://apucarana.pr.gov.br/pss/inscricao</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>404</v>
+      </c>
+      <c r="E118" t="n">
+        <v>4</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:28:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://compra.apucarana.pr.gov.br/services/strategy-planning/home</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>404</v>
+      </c>
+      <c r="E119" t="n">
+        <v>5</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:33:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>https://compra.apucarana.pr.gov.br/services/audit-evaluation/home</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>404</v>
+      </c>
+      <c r="E120" t="n">
+        <v>5</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:33:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>https://compra.apucarana.pr.gov.br/services/insurance/home</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>404</v>
+      </c>
+      <c r="E121" t="n">
+        <v>5</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:33:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>https://compra.apucarana.pr.gov.br/services/financial-services/home</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>404</v>
+      </c>
+      <c r="E122" t="n">
+        <v>5</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:33:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://compra.apucarana.pr.gov.br/services/communications/home</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>404</v>
+      </c>
+      <c r="E123" t="n">
+        <v>5</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:33:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>https://compra.apucarana.pr.gov.br/services/consumer-markets/home</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>404</v>
+      </c>
+      <c r="E124" t="n">
+        <v>5</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:34:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>http://portal.apucarana.pr.gov.br/pronimtb/index.asp?acao=1&amp;item=91&amp;visao=0</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
+        <v>5</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:41:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/autoatendimento</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>404</v>
+      </c>
+      <c r="E126" t="n">
+        <v>6</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:44:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>404</v>
+      </c>
+      <c r="E127" t="n">
+        <v>6</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:44:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos/certidao-negativa-de-debitos</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>404</v>
+      </c>
+      <c r="E128" t="n">
+        <v>6</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:44:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos/certidao-negativa-de-debitos/detalhar/1</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>404</v>
+      </c>
+      <c r="E129" t="n">
+        <v>6</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:45:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-issalvara</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>404</v>
+      </c>
+      <c r="E130" t="n">
+        <v>6</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:45:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-issalvara/detalhar/1</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>404</v>
+      </c>
+      <c r="E131" t="n">
+        <v>6</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:45:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-iptu</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>404</v>
+      </c>
+      <c r="E132" t="n">
+        <v>6</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:45:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-iptu/detalhar/1</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>404</v>
+      </c>
+      <c r="E133" t="n">
+        <v>6</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:45:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/site/servicos/nfs-e/Imh0dHBzOlwvXC9uZnNlLWFwdWNhcmFuYS5hdGVuZGUubmV0XC9hdXRvYXRlbmRpbWVudG9cLyI=</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>404</v>
+      </c>
+      <c r="E134" t="n">
+        <v>6</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:45:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos/consulta-de-licitacoes</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>404</v>
+      </c>
+      <c r="E135" t="n">
+        <v>6</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:45:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos/consulta-de-licitacoes/detalhar/1</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>404</v>
+      </c>
+      <c r="E136" t="n">
+        <v>6</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:45:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/@licitacaoapucarana6363/videos?view=0&amp;sort=dd&amp;shelf_id=1</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>404</v>
+      </c>
+      <c r="E137" t="n">
+        <v>6</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:45:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/watch?v=gruiYX3DvAo</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>404</v>
+      </c>
+      <c r="E138" t="n">
+        <v>6</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:46:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/sitemap</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>404</v>
+      </c>
+      <c r="E139" t="n">
+        <v>6</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:46:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Institucional/MISSAO-VISAO-DE-FUTURO-VALORES</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>404</v>
+      </c>
+      <c r="E140" t="n">
+        <v>6</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:46:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Institucional/QUEM-SOMOS-E-O-QUE-FAZEMOS</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>404</v>
+      </c>
+      <c r="E141" t="n">
+        <v>6</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:46:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Institucional/DIRETORIA</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>404</v>
+      </c>
+      <c r="E142" t="n">
+        <v>6</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:46:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Pagina/estatuto_social</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>404</v>
+      </c>
+      <c r="E143" t="n">
+        <v>6</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:46:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Pagina/GOVERNANCA-CORPORATIVA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>404</v>
+      </c>
+      <c r="E144" t="n">
+        <v>6</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:46:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Institucional/ATIVIDADES-DE-GESTAO</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>404</v>
+      </c>
+      <c r="E145" t="n">
+        <v>6</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:46:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Institucional/GESTAO-DE-RISCOS-E-GERENCIAMENTO-DE-CAPITAL</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>404</v>
+      </c>
+      <c r="E146" t="n">
+        <v>6</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:46:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Pagina/POLITICA-DE-RESPONSABILIDADE-SOCIOAMBIENTAL</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>404</v>
+      </c>
+      <c r="E147" t="n">
+        <v>6</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:46:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Microcredito-Facil</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>404</v>
+      </c>
+      <c r="E148" t="n">
+        <v>6</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:47:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Banco-da-Mulher-Paranaense/Microcredito</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>404</v>
+      </c>
+      <c r="E149" t="n">
+        <v>6</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:47:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Credito/Banco-da-Mulher-Paranaense/MPE</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>404</v>
+      </c>
+      <c r="E150" t="n">
+        <v>6</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:47:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Credito/BANCO-DO-EMPREENDEDOR</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>404</v>
+      </c>
+      <c r="E151" t="n">
+        <v>6</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:47:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Emprestimos</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>404</v>
+      </c>
+      <c r="E152" t="n">
+        <v>6</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:47:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Credito/AMPLIACAO-CONSTRUCAO-E-REFORMA</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>404</v>
+      </c>
+      <c r="E153" t="n">
+        <v>6</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:47:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Credito/MAQUINAS-E-EQUIPAMENTOS</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>404</v>
+      </c>
+      <c r="E154" t="n">
+        <v>6</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:47:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Credito/VEICULOS</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>404</v>
+      </c>
+      <c r="E155" t="n">
+        <v>6</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:47:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Credito/Energias-Renovaveis</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>404</v>
+      </c>
+      <c r="E156" t="n">
+        <v>6</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:47:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Credito/Fomento-Inova</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>404</v>
+      </c>
+      <c r="E157" t="n">
+        <v>6</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:48:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Credito/Recursos-BNDES</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>404</v>
+      </c>
+      <c r="E158" t="n">
+        <v>6</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:48:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Credito/FINANCIAMENTOS-AO-SETOR-PUBLICO</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>404</v>
+      </c>
+      <c r="E159" t="n">
+        <v>6</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:48:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Transparencia/Tabela-de-Tarifas</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>404</v>
+      </c>
+      <c r="E160" t="n">
+        <v>6</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:48:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Pagina/CUSTO-EFETIVO-TOTAL-CET</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>404</v>
+      </c>
+      <c r="E161" t="n">
+        <v>6</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:48:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Parcerias/AGENDA-DE-CURSOS</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>404</v>
+      </c>
+      <c r="E162" t="n">
+        <v>6</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:48:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Parcerias/AGENTES-DE-CREDITO</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>404</v>
+      </c>
+      <c r="E163" t="n">
+        <v>6</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:48:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Parcerias/SEJA-UM-AGENTE-DE-CREDITO</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>404</v>
+      </c>
+      <c r="E164" t="n">
+        <v>6</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:48:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Pagina/NOSSOS-CORRESPONDENTES</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>404</v>
+      </c>
+      <c r="E165" t="n">
+        <v>6</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:48:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Pagina/CORRESPONDENTES</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>404</v>
+      </c>
+      <c r="E166" t="n">
+        <v>6</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:49:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Pagina/COMO-SE-TORNAR-CORRESPONDENTE</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>404</v>
+      </c>
+      <c r="E167" t="n">
+        <v>6</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:49:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Pagina/Transparencia</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>404</v>
+      </c>
+      <c r="E168" t="n">
+        <v>6</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:49:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Transparencia/CONCURSOS-PUBLICOS</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>404</v>
+      </c>
+      <c r="E169" t="n">
+        <v>6</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:49:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Transparencia/Editais</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>404</v>
+      </c>
+      <c r="E170" t="n">
+        <v>6</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:49:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Transparencia/DEMONSTRATIVOS-CONTABEIS-FOMENTO-PARANA</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>404</v>
+      </c>
+      <c r="E171" t="n">
+        <v>6</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:49:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Fundos/DEMONSTRATIVOS-CONTABEIS-GESTAO-DE-FUNDOS</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>404</v>
+      </c>
+      <c r="E172" t="n">
+        <v>6</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:49:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/contatos</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>404</v>
+      </c>
+      <c r="E173" t="n">
+        <v>6</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:49:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-credito-para-micro-e-pequenas-empresas-JVN6AGoP</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>404</v>
+      </c>
+      <c r="E174" t="n">
+        <v>6</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:50:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-financiamento-ao-Banco-da-Mulher-Paranaense-aPo4dBom</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>404</v>
+      </c>
+      <c r="E175" t="n">
+        <v>6</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:50:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-microcredito-para-empreendedores-nQ3x0z32</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>404</v>
+      </c>
+      <c r="E176" t="n">
+        <v>6</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:50:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Empresa/Cadin/Consultar-se-o-CPF-ou-o-CNPJ-esta-inscrito-no-Cadin-aPo4ZB3m</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>404</v>
+      </c>
+      <c r="E177" t="n">
+        <v>6</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:50:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Mais-buscados/Certidoes/Emitir-Certidao-Negativa-Receita-Estadual-kZrX5gol</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>404</v>
+      </c>
+      <c r="E178" t="n">
+        <v>6</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:50:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Seguranca/Atestados-e-Certidoes/Solicitar-Atestado-de-Cadastro-Negativo-vGr5V6o0</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>404</v>
+      </c>
+      <c r="E179" t="n">
+        <v>6</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:50:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Servicos/Meio-Ambiente/Solicitar-licenciamento-ambiental-9OoqbNG0</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>404</v>
+      </c>
+      <c r="E180" t="n">
+        <v>6</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:50:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Receita-PR/Acesso-ao-portal/Acessar-o-Portal-Receita-PR-ybrz8JN4</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>404</v>
+      </c>
+      <c r="E181" t="n">
+        <v>6</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:50:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Administracao/Documentos/Cadastrar-se-no-PIA-6K3WwW3m</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>404</v>
+      </c>
+      <c r="E182" t="n">
+        <v>6</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:51:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Seguranca/Corpo-de-Bombeiros/Solicitar-analise-de-projeto-pelo-Corpo-de-Bombeiros-0GNAZ387</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>404</v>
+      </c>
+      <c r="E183" t="n">
+        <v>6</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:51:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Servicos/Municipios/Solicitar-financiamento-do-BRDE-kZrXMDol</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>404</v>
+      </c>
+      <c r="E184" t="n">
+        <v>6</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:51:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Servicos/Licenciamento/Solicitar-licenciamento-do-Corpo-de-Bombeiros-MD3PPn36</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>404</v>
+      </c>
+      <c r="E185" t="n">
+        <v>6</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:51:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Pagina/Ouvidoria</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>404</v>
+      </c>
+      <c r="E186" t="n">
+        <v>6</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:51:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/apucarana/</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>404</v>
+      </c>
+      <c r="E187" t="n">
+        <v>6</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:51:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/o-que-fazer/</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>404</v>
+      </c>
+      <c r="E188" t="n">
+        <v>6</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:51:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/onde-comer/</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>404</v>
+      </c>
+      <c r="E189" t="n">
+        <v>6</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:51:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/onde-ficar/</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>404</v>
+      </c>
+      <c r="E190" t="n">
+        <v>6</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:51:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/eventos/</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>404</v>
+      </c>
+      <c r="E191" t="n">
+        <v>6</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:52:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>404</v>
+      </c>
+      <c r="E192" t="n">
+        <v>6</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:52:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/ao-vivo/</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>404</v>
+      </c>
+      <c r="E193" t="n">
+        <v>6</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:52:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/travel-guide/conhecendo-apucarana</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>404</v>
+      </c>
+      <c r="E194" t="n">
+        <v>6</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:52:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/atrativos-da-serra/</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>404</v>
+      </c>
+      <c r="E195" t="n">
+        <v>6</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:52:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/noites-em-apucarana/</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>404</v>
+      </c>
+      <c r="E196" t="n">
+        <v>6</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:52:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/cafes-e-padarias/</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>404</v>
+      </c>
+      <c r="E197" t="n">
+        <v>6</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:52:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/natureza/</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>404</v>
+      </c>
+      <c r="E198" t="n">
+        <v>6</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:52:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/arte-cultura/</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>404</v>
+      </c>
+      <c r="E199" t="n">
+        <v>6</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:52:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/catedral-nossa-senhora-de-lourdes/</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>404</v>
+      </c>
+      <c r="E200" t="n">
+        <v>6</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:52:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/praca-rui-barbosa/</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>404</v>
+      </c>
+      <c r="E201" t="n">
+        <v>6</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:53:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/parque-jaboti/</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>404</v>
+      </c>
+      <c r="E202" t="n">
+        <v>6</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:53:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/espaco-das-feiras/</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>404</v>
+      </c>
+      <c r="E203" t="n">
+        <v>6</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:53:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/parque-ecologico-da-raposa/</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>404</v>
+      </c>
+      <c r="E204" t="n">
+        <v>6</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:53:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/praca-maua/</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>404</v>
+      </c>
+      <c r="E205" t="n">
+        <v>6</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:53:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/parque-da-redencao/</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>404</v>
+      </c>
+      <c r="E206" t="n">
+        <v>6</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:53:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/jardim-japones/</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>404</v>
+      </c>
+      <c r="E207" t="n">
+        <v>6</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:53:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/praca-da-onca/</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>404</v>
+      </c>
+      <c r="E208" t="n">
+        <v>6</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:53:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/bosque-municipal/</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>404</v>
+      </c>
+      <c r="E209" t="n">
+        <v>6</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:53:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/museu-do-cafe/</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>404</v>
+      </c>
+      <c r="E210" t="n">
+        <v>6</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:54:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/parque-ecologico-santo-expedito/</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>404</v>
+      </c>
+      <c r="E211" t="n">
+        <v>6</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:54:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/compre-roupas-direto-do-fabricante/</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>404</v>
+      </c>
+      <c r="E212" t="n">
+        <v>6</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:54:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/roteiro-da-fe/</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>404</v>
+      </c>
+      <c r="E213" t="n">
+        <v>6</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:54:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/roteiros-turisticos/</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>404</v>
+      </c>
+      <c r="E214" t="n">
+        <v>6</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:54:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/monumento-a-biblia/</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>404</v>
+      </c>
+      <c r="E215" t="n">
+        <v>6</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:54:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/monumento-ao-bone/</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>404</v>
+      </c>
+      <c r="E216" t="n">
+        <v>6</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:54:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/centro-civico/</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>404</v>
+      </c>
+      <c r="E217" t="n">
+        <v>6</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:54:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/memorial-casa-de-portugal-e-praca-jose-lebre-dos-santos/</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>404</v>
+      </c>
+      <c r="E218" t="n">
+        <v>6</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:54:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/exposicao-iconografica-josefina-mariana-e-marelliana/</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>404</v>
+      </c>
+      <c r="E219" t="n">
+        <v>6</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:54:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/praca-28-de-janeiro/</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>404</v>
+      </c>
+      <c r="E220" t="n">
+        <v>6</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:54:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/parque-biguacu/</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>404</v>
+      </c>
+      <c r="E221" t="n">
+        <v>6</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:55:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/museu-municipal-de-apucarana/</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>404</v>
+      </c>
+      <c r="E222" t="n">
+        <v>6</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:55:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/credenciamento/</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>404</v>
+      </c>
+      <c r="E223" t="n">
+        <v>6</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:55:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/multi.php</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>404</v>
+      </c>
+      <c r="E224" t="n">
+        <v>6</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:56:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/medica.php</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>404</v>
+      </c>
+      <c r="E225" t="n">
+        <v>6</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:56:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/editais.php</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>404</v>
+      </c>
+      <c r="E226" t="n">
+        <v>6</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:56:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/inscricoes.php</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>404</v>
+      </c>
+      <c r="E227" t="n">
+        <v>6</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:56:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/contato.php</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>404</v>
+      </c>
+      <c r="E228" t="n">
+        <v>6</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:56:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos/e-obituarios</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>404</v>
+      </c>
+      <c r="E229" t="n">
+        <v>6</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:56:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos/e-obituarios/detalhar/1</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>404</v>
+      </c>
+      <c r="E230" t="n">
+        <v>6</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:56:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/ame/calendario-2/)</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>404</v>
+      </c>
+      <c r="E231" t="n">
+        <v>8</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>2026-07-31 02:15:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/index.php</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>404</v>
+      </c>
+      <c r="E232" t="n">
+        <v>10</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>2026-07-31 02:40:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/multi.php</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>404</v>
+      </c>
+      <c r="E233" t="n">
+        <v>10</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>2026-07-31 02:40:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/medica.php</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>404</v>
+      </c>
+      <c r="E234" t="n">
+        <v>10</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>2026-07-31 02:40:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/editais.php</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>404</v>
+      </c>
+      <c r="E235" t="n">
+        <v>10</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>2026-07-31 02:40:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/inscricoes.php</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>404</v>
+      </c>
+      <c r="E236" t="n">
+        <v>10</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>2026-07-31 02:40:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/contato.php</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>404</v>
+      </c>
+      <c r="E237" t="n">
+        <v>10</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>2026-07-31 02:40:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/Transparencia/Editais</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>404</v>
+      </c>
+      <c r="E238" t="n">
+        <v>4</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>2026-07-31 02:44:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>https://www.apucarana.pr.gov.br/tour/jardim-japones/</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>404</v>
+      </c>
+      <c r="E239" t="n">
+        <v>4</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>2026-07-31 02:44:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>http://portal.apucarana.pr.gov.br/pronimtb/index.asp?acao=1&amp;item=91&amp;visao=0</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" t="n">
+        <v>5</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>2026-07-31 02:46:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>http://portal.apucarana.pr.gov.br/pronimtb/index.asp?acao=1&amp;item=91&amp;visao=0</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>0</v>
+      </c>
+      <c r="E241" t="n">
+        <v>5</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>2026-07-31 02:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-iptu</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>404</v>
+      </c>
+      <c r="E242" t="n">
+        <v>6</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>2026-07-31 02:50:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/sitemap</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>404</v>
+      </c>
+      <c r="E243" t="n">
+        <v>6</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>2026-07-31 02:50:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Institucional/MISSAO-VISAO-DE-FUTURO-VALORES</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>404</v>
+      </c>
+      <c r="E244" t="n">
+        <v>6</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>2026-07-31 02:50:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Credito/Recursos-BNDES</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>404</v>
+      </c>
+      <c r="E245" t="n">
+        <v>6</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>2026-07-31 02:50:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>404</v>
+      </c>
+      <c r="E246" t="n">
+        <v>6</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>2026-07-31 02:50:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/ao-vivo/</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>404</v>
+      </c>
+      <c r="E247" t="n">
+        <v>6</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>2026-07-31 02:50:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/travel-guide/conhecendo-apucarana</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>404</v>
+      </c>
+      <c r="E248" t="n">
+        <v>6</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>2026-07-31 02:50:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/roteiro-da-fe/</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>404</v>
+      </c>
+      <c r="E249" t="n">
+        <v>6</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>2026-07-31 02:51:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/monumento-a-biblia/</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>404</v>
+      </c>
+      <c r="E250" t="n">
+        <v>6</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>2026-07-31 02:51:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/monumento-ao-bone/</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>404</v>
+      </c>
+      <c r="E251" t="n">
+        <v>6</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>2026-07-31 02:51:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/centro-civico/</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>404</v>
+      </c>
+      <c r="E252" t="n">
+        <v>6</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>2026-07-31 02:51:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>https://apucarana.atende.net/transparencia/grupo/contas-publicas?agg=eyJncnVwbyI6IjEiLCJpZCI6IjlfMSJ9</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: SessionNotCreatedException</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>0</v>
+      </c>
+      <c r="E253" t="n">
+        <v>3</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>2026-07-31 03:45:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>https://apucarana.atende.net/transparencia/grupo/contas-publicas?agg=eyJncnVwbyI6IjEiLCJpZCI6IjdfMSJ9</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: SessionNotCreatedException</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>0</v>
+      </c>
+      <c r="E254" t="n">
+        <v>3</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>2026-07-31 03:45:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>https://apucarana.atende.net/?pg=rest&amp;service=WNERestServiceNFSe</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>HTTP_401</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>401</v>
+      </c>
+      <c r="E255" t="n">
+        <v>4</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>2026-07-31 04:14:46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/apucarana/erros_varredura.xlsx
+++ b/resultados/apucarana/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F255"/>
+  <dimension ref="A1:F408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-30 21:44:20</t>
+          <t>2026-08-03 05:39:04</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>http://compra.apucarana.pr.gov.br/contact/</t>
+          <t>https://www.apucarana.pr.gov.br/site/carta-de-servicos/programa-portas-abertas-cursos-profissionalizantes/</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-30 21:44:54</t>
+          <t>2026-08-03 05:39:10</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>http://apucarana.pr.gov.br/pss/inscricao</t>
+          <t>http://compra.apucarana.pr.gov.br/contact/</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -524,11 +524,11 @@
         <v>404</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-31 01:02:33</t>
+          <t>2026-08-03 05:40:01</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>http://sys.apucarana.pr.gov.br/apucarana-pr/uploads/madspot_1433631749.php</t>
+          <t>http://compra.apucarana.pr.gov.br/contact/</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -552,11 +552,11 @@
         <v>404</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-31 01:03:31</t>
+          <t>2026-08-03 05:40:10</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/site/carta-de-servicos/programa-portas-abertas-cursos-profissionalizantes/</t>
+          <t>https://www.apucarana.pr.gov.br/site/termos-de-busca/cadastro-de-emprego/</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -580,11 +580,11 @@
         <v>404</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-31 01:06:41</t>
+          <t>2026-08-03 09:11:48</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://compra.apucarana.pr.gov.br/services/strategy-planning/</t>
+          <t>http://apucarana.pr.gov.br/pss/inscricao</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -608,11 +608,11 @@
         <v>404</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-31 01:11:43</t>
+          <t>2026-08-03 09:14:34</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://compra.apucarana.pr.gov.br/services/audit-evaluation/</t>
+          <t>http://apucarana.pr.gov.br/pss/inscricao</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -636,11 +636,11 @@
         <v>404</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-31 01:11:50</t>
+          <t>2026-08-03 09:14:41</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://compra.apucarana.pr.gov.br/services/insurance/</t>
+          <t>http://sys.apucarana.pr.gov.br/apucarana-pr/uploads/madspot_1433631749.php</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -664,11 +664,11 @@
         <v>404</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-31 01:11:56</t>
+          <t>2026-08-03 09:15:32</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://compra.apucarana.pr.gov.br/services/financial-services/</t>
+          <t>http://www.apucarana.pr.gov.br/site/carta-de-servicos/programa-portas-abertas-cursos-profissionalizantes/</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-31 01:12:02</t>
+          <t>2026-08-03 09:43:37</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://compra.apucarana.pr.gov.br/services/communications/</t>
+          <t>http://www.apucarana.pr.gov.br/site/carta-de-servicos/programa-portas-abertas-cursos-profissionalizantes/</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-31 01:12:08</t>
+          <t>2026-08-03 09:43:52</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://compra.apucarana.pr.gov.br/services/consumer-markets/</t>
+          <t>https://compra.apucarana.pr.gov.br/services/strategy-planning/</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-31 01:12:14</t>
+          <t>2026-08-03 09:49:34</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/autoatendimento</t>
+          <t>https://compra.apucarana.pr.gov.br/services/strategy-planning/</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-31 01:15:21</t>
+          <t>2026-08-03 09:50:01</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos</t>
+          <t>https://compra.apucarana.pr.gov.br/services/audit-evaluation/</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-31 01:15:28</t>
+          <t>2026-08-03 09:50:02</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/certidao-negativa-de-debitos</t>
+          <t>https://compra.apucarana.pr.gov.br/services/audit-evaluation/</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-31 01:15:35</t>
+          <t>2026-08-03 09:50:11</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/certidao-negativa-de-debitos/detalhar/1</t>
+          <t>https://compra.apucarana.pr.gov.br/services/insurance/</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-31 01:15:43</t>
+          <t>2026-08-03 09:50:12</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-issalvara</t>
+          <t>https://compra.apucarana.pr.gov.br/services/insurance/</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-31 01:15:50</t>
+          <t>2026-08-03 09:50:42</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-issalvara/detalhar/1</t>
+          <t>https://compra.apucarana.pr.gov.br/services/financial-services/</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-31 01:15:57</t>
+          <t>2026-08-03 09:50:44</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-iptu</t>
+          <t>https://compra.apucarana.pr.gov.br/services/financial-services/</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-31 01:16:04</t>
+          <t>2026-08-03 09:50:59</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-iptu/detalhar/1</t>
+          <t>https://compra.apucarana.pr.gov.br/services/communications/</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-31 01:16:11</t>
+          <t>2026-08-03 09:51:00</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/site/servicos/nfs-e/Imh0dHBzOlwvXC9uZnNlLWFwdWNhcmFuYS5hdGVuZGUubmV0XC9hdXRvYXRlbmRpbWVudG9cLyI=</t>
+          <t>https://compra.apucarana.pr.gov.br/services/communications/</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-31 01:16:20</t>
+          <t>2026-08-03 09:51:11</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/consulta-de-licitacoes</t>
+          <t>https://compra.apucarana.pr.gov.br/services/consumer-markets/</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-31 01:16:26</t>
+          <t>2026-08-03 09:51:12</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/consulta-de-licitacoes/detalhar/1</t>
+          <t>https://compra.apucarana.pr.gov.br/services/consumer-markets/</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-31 01:16:33</t>
+          <t>2026-08-03 09:51:42</t>
         </is>
       </c>
     </row>
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/@licitacaoapucarana6363/videos?view=0&amp;sort=dd&amp;shelf_id=1</t>
+          <t>https://www.apucarana.pr.gov.br/site/servicos/regularizacao-do-rotativo/</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-31 01:16:41</t>
+          <t>2026-08-03 10:01:12</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/watch?v=gruiYX3DvAo</t>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-31 01:16:48</t>
+          <t>2026-08-03 10:01:30</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/sitemap</t>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-31 01:16:55</t>
+          <t>2026-08-03 10:01:45</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Institucional/MISSAO-VISAO-DE-FUTURO-VALORES</t>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-31 01:17:02</t>
+          <t>2026-08-03 10:01:45</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Institucional/QUEM-SOMOS-E-O-QUE-FAZEMOS</t>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-31 01:17:10</t>
+          <t>2026-08-03 10:02:02</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Institucional/DIRETORIA</t>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/certidao-negativa-de-debitos</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-31 01:17:17</t>
+          <t>2026-08-03 10:02:02</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Pagina/estatuto_social</t>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/certidao-negativa-de-debitos</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-31 01:17:24</t>
+          <t>2026-08-03 10:02:34</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Pagina/GOVERNANCA-CORPORATIVA</t>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/certidao-negativa-de-debitos/detalhar/1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-31 01:17:31</t>
+          <t>2026-08-03 10:02:35</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Institucional/ATIVIDADES-DE-GESTAO</t>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-issalvara</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-31 01:17:38</t>
+          <t>2026-08-03 10:03:09</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Institucional/GESTAO-DE-RISCOS-E-GERENCIAMENTO-DE-CAPITAL</t>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-issalvara</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-31 01:17:46</t>
+          <t>2026-08-03 10:03:20</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Pagina/POLITICA-DE-RESPONSABILIDADE-SOCIOAMBIENTAL</t>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-issalvara/detalhar/1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-31 01:17:53</t>
+          <t>2026-08-03 10:03:20</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Microcredito-Facil</t>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-issalvara/detalhar/1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-31 01:18:00</t>
+          <t>2026-08-03 10:03:30</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Banco-da-Mulher-Paranaense/Microcredito</t>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-iptu</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-31 01:18:07</t>
+          <t>2026-08-03 10:03:31</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Credito/Banco-da-Mulher-Paranaense/MPE</t>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-iptu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-31 01:18:14</t>
+          <t>2026-08-03 10:03:44</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Credito/BANCO-DO-EMPREENDEDOR</t>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-iptu/detalhar/1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-31 01:18:22</t>
+          <t>2026-08-03 10:03:44</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Emprestimos</t>
+          <t>https://www.apucarana.pr.gov.br/site/servicos/nfs-e/Imh0dHBzOlwvXC9uZnNlLWFwdWNhcmFuYS5hdGVuZGUubmV0XC9hdXRvYXRlbmRpbWVudG9cLyI=</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-31 01:18:29</t>
+          <t>2026-08-03 10:04:20</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Credito/AMPLIACAO-CONSTRUCAO-E-REFORMA</t>
+          <t>https://www.apucarana.pr.gov.br/site/servicos/nfs-e/Imh0dHBzOlwvXC9uZnNlLWFwdWNhcmFuYS5hdGVuZGUubmV0XC9hdXRvYXRlbmRpbWVudG9cLyI=</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-31 01:18:36</t>
+          <t>2026-08-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Credito/MAQUINAS-E-EQUIPAMENTOS</t>
+          <t>https://www.apucarana.pr.gov.br/@licitacaoapucarana6363/videos?view=0&amp;sort=dd&amp;shelf_id=1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-31 01:18:43</t>
+          <t>2026-08-03 10:04:25</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Credito/VEICULOS</t>
+          <t>https://www.apucarana.pr.gov.br/@licitacaoapucarana6363/videos?view=0&amp;sort=dd&amp;shelf_id=1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-31 01:18:51</t>
+          <t>2026-08-03 10:04:55</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Credito/Energias-Renovaveis</t>
+          <t>https://www.apucarana.pr.gov.br/watch?v=gruiYX3DvAo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-31 01:18:58</t>
+          <t>2026-08-03 10:04:55</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Credito/Fomento-Inova</t>
+          <t>https://www.apucarana.pr.gov.br/watch?v=gruiYX3DvAo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-31 01:19:05</t>
+          <t>2026-08-03 10:05:19</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Credito/Recursos-BNDES</t>
+          <t>https://www.apucarana.pr.gov.br/sitemap</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-31 01:19:15</t>
+          <t>2026-08-03 10:05:19</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Credito/FINANCIAMENTOS-AO-SETOR-PUBLICO</t>
+          <t>https://www.apucarana.pr.gov.br/sitemap</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-31 01:19:22</t>
+          <t>2026-08-03 10:05:50</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Transparencia/Tabela-de-Tarifas</t>
+          <t>https://www.apucarana.pr.gov.br/Institucional/MISSAO-VISAO-DE-FUTURO-VALORES</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-31 01:19:29</t>
+          <t>2026-08-03 10:05:50</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Pagina/CUSTO-EFETIVO-TOTAL-CET</t>
+          <t>https://www.apucarana.pr.gov.br/Institucional/QUEM-SOMOS-E-O-QUE-FAZEMOS</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-31 01:19:36</t>
+          <t>2026-08-03 10:06:25</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Parcerias/AGENDA-DE-CURSOS</t>
+          <t>https://www.apucarana.pr.gov.br/Institucional/QUEM-SOMOS-E-O-QUE-FAZEMOS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-31 01:19:44</t>
+          <t>2026-08-03 10:06:32</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Parcerias/AGENTES-DE-CREDITO</t>
+          <t>https://www.apucarana.pr.gov.br/Institucional/DIRETORIA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-31 01:19:51</t>
+          <t>2026-08-03 10:06:33</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Parcerias/SEJA-UM-AGENTE-DE-CREDITO</t>
+          <t>https://www.apucarana.pr.gov.br/Institucional/DIRETORIA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-31 01:19:58</t>
+          <t>2026-08-03 10:06:47</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Pagina/NOSSOS-CORRESPONDENTES</t>
+          <t>https://www.apucarana.pr.gov.br/Pagina/estatuto_social</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-31 01:20:05</t>
+          <t>2026-08-03 10:06:49</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Pagina/CORRESPONDENTES</t>
+          <t>https://www.apucarana.pr.gov.br/Pagina/estatuto_social</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-31 01:20:15</t>
+          <t>2026-08-03 10:07:23</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Pagina/COMO-SE-TORNAR-CORRESPONDENTE</t>
+          <t>https://www.apucarana.pr.gov.br/Pagina/GOVERNANCA-CORPORATIVA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-31 01:20:22</t>
+          <t>2026-08-03 10:07:23</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Pagina/Transparencia</t>
+          <t>https://www.apucarana.pr.gov.br/Pagina/GOVERNANCA-CORPORATIVA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-31 01:20:29</t>
+          <t>2026-08-03 10:07:40</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Transparencia/CONCURSOS-PUBLICOS</t>
+          <t>https://www.apucarana.pr.gov.br/Institucional/ATIVIDADES-DE-GESTAO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-31 01:20:36</t>
+          <t>2026-08-03 10:07:40</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Transparencia/Editais</t>
+          <t>https://www.apucarana.pr.gov.br/Institucional/ATIVIDADES-DE-GESTAO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-31 01:20:46</t>
+          <t>2026-08-03 10:08:08</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Transparencia/DEMONSTRATIVOS-CONTABEIS-FOMENTO-PARANA</t>
+          <t>https://www.apucarana.pr.gov.br/Institucional/GESTAO-DE-RISCOS-E-GERENCIAMENTO-DE-CAPITAL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-31 01:20:49</t>
+          <t>2026-08-03 10:08:08</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Fundos/DEMONSTRATIVOS-CONTABEIS-GESTAO-DE-FUNDOS</t>
+          <t>https://www.apucarana.pr.gov.br/Institucional/GESTAO-DE-RISCOS-E-GERENCIAMENTO-DE-CAPITAL</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-31 01:20:56</t>
+          <t>2026-08-03 10:08:12</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/contatos</t>
+          <t>https://www.apucarana.pr.gov.br/Pagina/POLITICA-DE-RESPONSABILIDADE-SOCIOAMBIENTAL</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-31 01:21:03</t>
+          <t>2026-08-03 10:08:13</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-credito-para-micro-e-pequenas-empresas-JVN6AGoP</t>
+          <t>https://www.apucarana.pr.gov.br/Pagina/POLITICA-DE-RESPONSABILIDADE-SOCIOAMBIENTAL</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-31 01:21:10</t>
+          <t>2026-08-03 10:08:17</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-financiamento-ao-Banco-da-Mulher-Paranaense-aPo4dBom</t>
+          <t>https://www.apucarana.pr.gov.br/Microcredito-Facil</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-31 01:21:18</t>
+          <t>2026-08-03 10:08:17</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-microcredito-para-empreendedores-nQ3x0z32</t>
+          <t>https://www.apucarana.pr.gov.br/Microcredito-Facil</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-31 01:21:25</t>
+          <t>2026-08-03 10:08:21</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/servicos/Empresa/Cadin/Consultar-se-o-CPF-ou-o-CNPJ-esta-inscrito-no-Cadin-aPo4ZB3m</t>
+          <t>https://www.apucarana.pr.gov.br/Banco-da-Mulher-Paranaense/Microcredito</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-31 01:21:32</t>
+          <t>2026-08-03 10:08:21</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/servicos/Mais-buscados/Certidoes/Emitir-Certidao-Negativa-Receita-Estadual-kZrX5gol</t>
+          <t>https://www.apucarana.pr.gov.br/Banco-da-Mulher-Paranaense/Microcredito</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-31 01:21:39</t>
+          <t>2026-08-03 10:08:25</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/servicos/Seguranca/Atestados-e-Certidoes/Solicitar-Atestado-de-Cadastro-Negativo-vGr5V6o0</t>
+          <t>https://www.apucarana.pr.gov.br/Credito/Banco-da-Mulher-Paranaense/MPE</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-31 01:21:47</t>
+          <t>2026-08-03 10:08:25</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/servicos/Servicos/Meio-Ambiente/Solicitar-licenciamento-ambiental-9OoqbNG0</t>
+          <t>https://www.apucarana.pr.gov.br/Credito/BANCO-DO-EMPREENDEDOR</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-31 01:21:54</t>
+          <t>2026-08-03 10:08:59</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/servicos/Receita-PR/Acesso-ao-portal/Acessar-o-Portal-Receita-PR-ybrz8JN4</t>
+          <t>https://www.apucarana.pr.gov.br/Credito/BANCO-DO-EMPREENDEDOR</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-31 01:22:01</t>
+          <t>2026-08-03 10:09:10</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/servicos/Administracao/Documentos/Cadastrar-se-no-PIA-6K3WwW3m</t>
+          <t>https://www.apucarana.pr.gov.br/Emprestimos</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-31 01:22:08</t>
+          <t>2026-08-03 10:09:10</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/servicos/Seguranca/Corpo-de-Bombeiros/Solicitar-analise-de-projeto-pelo-Corpo-de-Bombeiros-0GNAZ387</t>
+          <t>https://www.apucarana.pr.gov.br/Emprestimos</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-31 01:22:16</t>
+          <t>2026-08-03 10:09:43</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/servicos/Servicos/Municipios/Solicitar-financiamento-do-BRDE-kZrXMDol</t>
+          <t>https://www.apucarana.pr.gov.br/Credito/AMPLIACAO-CONSTRUCAO-E-REFORMA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-31 01:22:23</t>
+          <t>2026-08-03 10:09:43</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/servicos/Servicos/Licenciamento/Solicitar-licenciamento-do-Corpo-de-Bombeiros-MD3PPn36</t>
+          <t>https://www.apucarana.pr.gov.br/Credito/AMPLIACAO-CONSTRUCAO-E-REFORMA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-31 01:22:30</t>
+          <t>2026-08-03 10:09:59</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Pagina/Ouvidoria</t>
+          <t>https://www.apucarana.pr.gov.br/Credito/MAQUINAS-E-EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-31 01:22:37</t>
+          <t>2026-08-03 10:09:59</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/apucarana/</t>
+          <t>https://www.apucarana.pr.gov.br/Credito/MAQUINAS-E-EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-31 01:22:44</t>
+          <t>2026-08-03 10:10:03</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/o-que-fazer/</t>
+          <t>https://www.apucarana.pr.gov.br/Credito/VEICULOS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-31 01:22:52</t>
+          <t>2026-08-03 10:10:04</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/onde-comer/</t>
+          <t>https://www.apucarana.pr.gov.br/Credito/VEICULOS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-31 01:22:59</t>
+          <t>2026-08-03 10:10:34</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/onde-ficar/</t>
+          <t>https://www.apucarana.pr.gov.br/Credito/Energias-Renovaveis</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-31 01:23:06</t>
+          <t>2026-08-03 10:10:34</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/eventos/</t>
+          <t>https://www.apucarana.pr.gov.br/Credito/Energias-Renovaveis</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-31 01:23:14</t>
+          <t>2026-08-03 10:10:54</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/servicos/</t>
+          <t>https://www.apucarana.pr.gov.br/Credito/Fomento-Inova</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-31 01:23:21</t>
+          <t>2026-08-03 10:10:54</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/ao-vivo/</t>
+          <t>https://www.apucarana.pr.gov.br/Credito/Fomento-Inova</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-31 01:23:28</t>
+          <t>2026-08-03 10:10:59</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/travel-guide/conhecendo-apucarana</t>
+          <t>https://www.apucarana.pr.gov.br/Credito/Recursos-BNDES</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-31 01:23:35</t>
+          <t>2026-08-03 10:10:59</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/atrativos-da-serra/</t>
+          <t>https://www.apucarana.pr.gov.br/Credito/Recursos-BNDES</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-31 01:23:42</t>
+          <t>2026-08-03 10:11:21</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/noites-em-apucarana/</t>
+          <t>https://www.apucarana.pr.gov.br/Credito/FINANCIAMENTOS-AO-SETOR-PUBLICO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-31 01:23:50</t>
+          <t>2026-08-03 10:11:21</t>
         </is>
       </c>
     </row>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/cafes-e-padarias/</t>
+          <t>https://www.apucarana.pr.gov.br/Credito/FINANCIAMENTOS-AO-SETOR-PUBLICO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-31 01:23:57</t>
+          <t>2026-08-03 10:11:37</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/natureza/</t>
+          <t>https://www.apucarana.pr.gov.br/Transparencia/Tabela-de-Tarifas</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-31 01:24:04</t>
+          <t>2026-08-03 10:11:38</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/arte-cultura/</t>
+          <t>https://www.apucarana.pr.gov.br/Pagina/CUSTO-EFETIVO-TOTAL-CET</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-31 01:24:11</t>
+          <t>2026-08-03 10:12:12</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/tour/catedral-nossa-senhora-de-lourdes/</t>
+          <t>https://www.apucarana.pr.gov.br/Pagina/CUSTO-EFETIVO-TOTAL-CET</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-31 01:24:19</t>
+          <t>2026-08-03 10:12:17</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/tour/praca-rui-barbosa/</t>
+          <t>https://www.apucarana.pr.gov.br/Parcerias/AGENDA-DE-CURSOS</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-31 01:24:26</t>
+          <t>2026-08-03 10:12:17</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/tour/parque-jaboti/</t>
+          <t>https://www.apucarana.pr.gov.br/Parcerias/AGENDA-DE-CURSOS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-31 01:24:33</t>
+          <t>2026-08-03 10:12:22</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/tour/espaco-das-feiras/</t>
+          <t>https://www.apucarana.pr.gov.br/Parcerias/AGENTES-DE-CREDITO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-31 01:24:40</t>
+          <t>2026-08-03 10:12:22</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/tour/parque-ecologico-da-raposa/</t>
+          <t>https://www.apucarana.pr.gov.br/Parcerias/AGENTES-DE-CREDITO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-31 01:24:47</t>
+          <t>2026-08-03 10:12:26</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/tour/praca-maua/</t>
+          <t>https://www.apucarana.pr.gov.br/Parcerias/SEJA-UM-AGENTE-DE-CREDITO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-31 01:24:55</t>
+          <t>2026-08-03 10:12:26</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/tour/parque-da-redencao/</t>
+          <t>https://www.apucarana.pr.gov.br/Pagina/NOSSOS-CORRESPONDENTES</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-31 01:25:02</t>
+          <t>2026-08-03 10:13:00</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/tour/jardim-japones/</t>
+          <t>https://www.apucarana.pr.gov.br/Pagina/NOSSOS-CORRESPONDENTES</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-31 01:25:09</t>
+          <t>2026-08-03 10:13:08</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/tour/praca-da-onca/</t>
+          <t>https://www.apucarana.pr.gov.br/Pagina/CORRESPONDENTES</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-31 01:25:12</t>
+          <t>2026-08-03 10:13:08</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/tour/bosque-municipal/</t>
+          <t>https://www.apucarana.pr.gov.br/Pagina/CORRESPONDENTES</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-31 01:25:20</t>
+          <t>2026-08-03 10:13:12</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/tour/museu-do-cafe/</t>
+          <t>https://www.apucarana.pr.gov.br/Pagina/COMO-SE-TORNAR-CORRESPONDENTE</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-31 01:25:27</t>
+          <t>2026-08-03 10:13:12</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/tour/parque-ecologico-santo-expedito/</t>
+          <t>https://www.apucarana.pr.gov.br/Pagina/COMO-SE-TORNAR-CORRESPONDENTE</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-31 01:25:34</t>
+          <t>2026-08-03 10:13:16</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/compre-roupas-direto-do-fabricante/</t>
+          <t>https://www.apucarana.pr.gov.br/Pagina/Transparencia</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-31 01:25:41</t>
+          <t>2026-08-03 10:13:16</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/roteiro-da-fe/</t>
+          <t>https://www.apucarana.pr.gov.br/Transparencia/CONCURSOS-PUBLICOS</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-31 01:25:49</t>
+          <t>2026-08-03 10:13:51</t>
         </is>
       </c>
     </row>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/roteiros-turisticos/</t>
+          <t>https://www.apucarana.pr.gov.br/Transparencia/CONCURSOS-PUBLICOS</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-31 01:25:56</t>
+          <t>2026-08-03 10:13:58</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/tour/monumento-a-biblia/</t>
+          <t>https://www.apucarana.pr.gov.br/Transparencia/Editais</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-31 01:26:03</t>
+          <t>2026-08-03 10:13:58</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/tour/monumento-ao-bone/</t>
+          <t>https://www.apucarana.pr.gov.br/Transparencia/Editais</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-31 01:26:11</t>
+          <t>2026-08-03 10:14:02</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/tour/centro-civico/</t>
+          <t>https://www.apucarana.pr.gov.br/Transparencia/DEMONSTRATIVOS-CONTABEIS-FOMENTO-PARANA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-31 01:26:18</t>
+          <t>2026-08-03 10:14:03</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/tour/memorial-casa-de-portugal-e-praca-jose-lebre-dos-santos/</t>
+          <t>https://www.apucarana.pr.gov.br/Transparencia/DEMONSTRATIVOS-CONTABEIS-FOMENTO-PARANA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-31 01:26:25</t>
+          <t>2026-08-03 10:14:07</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/tour/exposicao-iconografica-josefina-mariana-e-marelliana/</t>
+          <t>https://www.apucarana.pr.gov.br/Fundos/DEMONSTRATIVOS-CONTABEIS-GESTAO-DE-FUNDOS</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-31 01:26:33</t>
+          <t>2026-08-03 10:14:07</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/tour/praca-28-de-janeiro/</t>
+          <t>https://www.apucarana.pr.gov.br/Fundos/DEMONSTRATIVOS-CONTABEIS-GESTAO-DE-FUNDOS</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-31 01:26:40</t>
+          <t>2026-08-03 10:14:11</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/tour/parque-biguacu/</t>
+          <t>https://www.apucarana.pr.gov.br/contatos</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-31 01:26:47</t>
+          <t>2026-08-03 10:14:11</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/tour/museu-municipal-de-apucarana/</t>
+          <t>https://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-credito-para-micro-e-pequenas-empresas-JVN6AGoP</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-31 01:26:54</t>
+          <t>2026-08-03 10:14:45</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/credenciamento/</t>
+          <t>https://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-credito-para-micro-e-pequenas-empresas-JVN6AGoP</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-31 01:27:02</t>
+          <t>2026-08-03 10:14:57</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/multi.php</t>
+          <t>https://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-financiamento-ao-Banco-da-Mulher-Paranaense-aPo4dBom</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-31 01:27:41</t>
+          <t>2026-08-03 10:14:57</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/medica.php</t>
+          <t>https://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-financiamento-ao-Banco-da-Mulher-Paranaense-aPo4dBom</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-31 01:27:47</t>
+          <t>2026-08-03 10:15:29</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/editais.php</t>
+          <t>https://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-microcredito-para-empreendedores-nQ3x0z32</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-31 01:27:54</t>
+          <t>2026-08-03 10:15:30</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/inscricoes.php</t>
+          <t>https://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-microcredito-para-empreendedores-nQ3x0z32</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-31 01:28:01</t>
+          <t>2026-08-03 10:15:48</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/contato.php</t>
+          <t>https://www.apucarana.pr.gov.br/servicos/Empresa/Cadin/Consultar-se-o-CPF-ou-o-CNPJ-esta-inscrito-no-Cadin-aPo4ZB3m</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-31 01:28:07</t>
+          <t>2026-08-03 10:15:48</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/e-obituarios</t>
+          <t>https://www.apucarana.pr.gov.br/servicos/Mais-buscados/Certidoes/Emitir-Certidao-Negativa-Receita-Estadual-kZrX5gol</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-31 01:28:13</t>
+          <t>2026-08-03 10:16:23</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/e-obituarios/detalhar/1</t>
+          <t>https://www.apucarana.pr.gov.br/servicos/Mais-buscados/Certidoes/Emitir-Certidao-Negativa-Receita-Estadual-kZrX5gol</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-31 01:28:20</t>
+          <t>2026-08-03 10:16:34</t>
         </is>
       </c>
     </row>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://apucarana.pr.gov.br/pss/inscricao</t>
+          <t>https://www.apucarana.pr.gov.br/servicos/Seguranca/Atestados-e-Certidoes/Solicitar-Atestado-de-Cadastro-Negativo-vGr5V6o0</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-31 01:28:39</t>
+          <t>2026-08-03 10:16:34</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://compra.apucarana.pr.gov.br/services/strategy-planning/home</t>
+          <t>https://www.apucarana.pr.gov.br/servicos/Seguranca/Atestados-e-Certidoes/Solicitar-Atestado-de-Cadastro-Negativo-vGr5V6o0</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3744,11 +3744,11 @@
         <v>404</v>
       </c>
       <c r="E119" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-07-31 01:33:30</t>
+          <t>2026-08-03 10:16:38</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://compra.apucarana.pr.gov.br/services/audit-evaluation/home</t>
+          <t>https://www.apucarana.pr.gov.br/servicos/Servicos/Meio-Ambiente/Solicitar-licenciamento-ambiental-9OoqbNG0</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3772,11 +3772,11 @@
         <v>404</v>
       </c>
       <c r="E120" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-07-31 01:33:37</t>
+          <t>2026-08-03 10:16:39</t>
         </is>
       </c>
     </row>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://compra.apucarana.pr.gov.br/services/insurance/home</t>
+          <t>https://www.apucarana.pr.gov.br/servicos/Receita-PR/Acesso-ao-portal/Acessar-o-Portal-Receita-PR-ybrz8JN4</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3800,11 +3800,11 @@
         <v>404</v>
       </c>
       <c r="E121" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-07-31 01:33:43</t>
+          <t>2026-08-03 10:17:15</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://compra.apucarana.pr.gov.br/services/financial-services/home</t>
+          <t>https://www.apucarana.pr.gov.br/servicos/Receita-PR/Acesso-ao-portal/Acessar-o-Portal-Receita-PR-ybrz8JN4</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3828,11 +3828,11 @@
         <v>404</v>
       </c>
       <c r="E122" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-07-31 01:33:49</t>
+          <t>2026-08-03 10:17:24</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://compra.apucarana.pr.gov.br/services/communications/home</t>
+          <t>https://www.apucarana.pr.gov.br/servicos/Administracao/Documentos/Cadastrar-se-no-PIA-6K3WwW3m</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3856,11 +3856,11 @@
         <v>404</v>
       </c>
       <c r="E123" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-07-31 01:33:55</t>
+          <t>2026-08-03 10:17:24</t>
         </is>
       </c>
     </row>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://compra.apucarana.pr.gov.br/services/consumer-markets/home</t>
+          <t>https://www.apucarana.pr.gov.br/servicos/Administracao/Documentos/Cadastrar-se-no-PIA-6K3WwW3m</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3884,11 +3884,11 @@
         <v>404</v>
       </c>
       <c r="E124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-07-31 01:34:02</t>
+          <t>2026-08-03 10:17:30</t>
         </is>
       </c>
     </row>
@@ -3900,23 +3900,23 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>http://portal.apucarana.pr.gov.br/pronimtb/index.asp?acao=1&amp;item=91&amp;visao=0</t>
+          <t>https://www.apucarana.pr.gov.br/servicos/Seguranca/Corpo-de-Bombeiros/Solicitar-analise-de-projeto-pelo-Corpo-de-Bombeiros-0GNAZ387</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E125" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-31 01:41:30</t>
+          <t>2026-08-03 10:17:30</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/autoatendimento</t>
+          <t>https://www.apucarana.pr.gov.br/servicos/Seguranca/Corpo-de-Bombeiros/Solicitar-analise-de-projeto-pelo-Corpo-de-Bombeiros-0GNAZ387</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3940,11 +3940,11 @@
         <v>404</v>
       </c>
       <c r="E126" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-07-31 01:44:39</t>
+          <t>2026-08-03 10:17:55</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos</t>
+          <t>https://www.apucarana.pr.gov.br/servicos/Servicos/Municipios/Solicitar-financiamento-do-BRDE-kZrXMDol</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3968,11 +3968,11 @@
         <v>404</v>
       </c>
       <c r="E127" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-07-31 01:44:48</t>
+          <t>2026-08-03 10:17:55</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos/certidao-negativa-de-debitos</t>
+          <t>https://www.apucarana.pr.gov.br/servicos/Servicos/Municipios/Solicitar-financiamento-do-BRDE-kZrXMDol</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3996,11 +3996,11 @@
         <v>404</v>
       </c>
       <c r="E128" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-07-31 01:44:55</t>
+          <t>2026-08-03 10:18:14</t>
         </is>
       </c>
     </row>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos/certidao-negativa-de-debitos/detalhar/1</t>
+          <t>https://www.apucarana.pr.gov.br/servicos/Servicos/Licenciamento/Solicitar-licenciamento-do-Corpo-de-Bombeiros-MD3PPn36</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4024,11 +4024,11 @@
         <v>404</v>
       </c>
       <c r="E129" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-07-31 01:45:02</t>
+          <t>2026-08-03 10:18:15</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-issalvara</t>
+          <t>https://www.apucarana.pr.gov.br/Pagina/Ouvidoria</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4052,11 +4052,11 @@
         <v>404</v>
       </c>
       <c r="E130" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-07-31 01:45:10</t>
+          <t>2026-08-03 10:18:49</t>
         </is>
       </c>
     </row>
@@ -4068,7 +4068,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-issalvara/detalhar/1</t>
+          <t>https://www.apucarana.pr.gov.br/Pagina/Ouvidoria</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4080,11 +4080,11 @@
         <v>404</v>
       </c>
       <c r="E131" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-07-31 01:45:17</t>
+          <t>2026-08-03 10:18:59</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-iptu</t>
+          <t>https://www.apucarana.pr.gov.br/apucarana/</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4108,11 +4108,11 @@
         <v>404</v>
       </c>
       <c r="E132" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-07-31 01:45:24</t>
+          <t>2026-08-03 10:18:59</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-iptu/detalhar/1</t>
+          <t>https://www.apucarana.pr.gov.br/apucarana/</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4136,11 +4136,11 @@
         <v>404</v>
       </c>
       <c r="E133" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-07-31 01:45:25</t>
+          <t>2026-08-03 10:19:05</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/site/servicos/nfs-e/Imh0dHBzOlwvXC9uZnNlLWFwdWNhcmFuYS5hdGVuZGUubmV0XC9hdXRvYXRlbmRpbWVudG9cLyI=</t>
+          <t>https://www.apucarana.pr.gov.br/o-que-fazer/</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4164,11 +4164,11 @@
         <v>404</v>
       </c>
       <c r="E134" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-07-31 01:45:34</t>
+          <t>2026-08-03 10:19:06</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos/consulta-de-licitacoes</t>
+          <t>https://www.apucarana.pr.gov.br/onde-comer/</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4192,11 +4192,11 @@
         <v>404</v>
       </c>
       <c r="E135" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-07-31 01:45:39</t>
+          <t>2026-08-03 10:19:40</t>
         </is>
       </c>
     </row>
@@ -4208,7 +4208,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos/consulta-de-licitacoes/detalhar/1</t>
+          <t>https://www.apucarana.pr.gov.br/onde-comer/</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4220,11 +4220,11 @@
         <v>404</v>
       </c>
       <c r="E136" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-07-31 01:45:46</t>
+          <t>2026-08-03 10:19:48</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/@licitacaoapucarana6363/videos?view=0&amp;sort=dd&amp;shelf_id=1</t>
+          <t>https://www.apucarana.pr.gov.br/onde-ficar/</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4248,11 +4248,11 @@
         <v>404</v>
       </c>
       <c r="E137" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-07-31 01:45:54</t>
+          <t>2026-08-03 10:19:48</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/watch?v=gruiYX3DvAo</t>
+          <t>https://www.apucarana.pr.gov.br/onde-ficar/</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4276,11 +4276,11 @@
         <v>404</v>
       </c>
       <c r="E138" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-07-31 01:46:01</t>
+          <t>2026-08-03 10:19:52</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/sitemap</t>
+          <t>https://www.apucarana.pr.gov.br/eventos/</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4304,11 +4304,11 @@
         <v>404</v>
       </c>
       <c r="E139" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-07-31 01:46:08</t>
+          <t>2026-08-03 10:19:53</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Institucional/MISSAO-VISAO-DE-FUTURO-VALORES</t>
+          <t>https://www.apucarana.pr.gov.br/eventos/</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4332,11 +4332,11 @@
         <v>404</v>
       </c>
       <c r="E140" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-07-31 01:46:09</t>
+          <t>2026-08-03 10:19:57</t>
         </is>
       </c>
     </row>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Institucional/QUEM-SOMOS-E-O-QUE-FAZEMOS</t>
+          <t>https://www.apucarana.pr.gov.br/servicos/</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4360,11 +4360,11 @@
         <v>404</v>
       </c>
       <c r="E141" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-07-31 01:46:10</t>
+          <t>2026-08-03 10:19:57</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Institucional/DIRETORIA</t>
+          <t>https://www.apucarana.pr.gov.br/servicos/</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4388,11 +4388,11 @@
         <v>404</v>
       </c>
       <c r="E142" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-07-31 01:46:17</t>
+          <t>2026-08-03 10:20:12</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Pagina/estatuto_social</t>
+          <t>https://www.apucarana.pr.gov.br/ao-vivo/</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4416,11 +4416,11 @@
         <v>404</v>
       </c>
       <c r="E143" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-07-31 01:46:24</t>
+          <t>2026-08-03 10:20:12</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Pagina/GOVERNANCA-CORPORATIVA</t>
+          <t>https://www.apucarana.pr.gov.br/ao-vivo/</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4444,11 +4444,11 @@
         <v>404</v>
       </c>
       <c r="E144" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-07-31 01:46:31</t>
+          <t>2026-08-03 10:20:46</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Institucional/ATIVIDADES-DE-GESTAO</t>
+          <t>https://www.apucarana.pr.gov.br/travel-guide/conhecendo-apucarana</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4472,11 +4472,11 @@
         <v>404</v>
       </c>
       <c r="E145" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-07-31 01:46:39</t>
+          <t>2026-08-03 10:20:46</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Institucional/GESTAO-DE-RISCOS-E-GERENCIAMENTO-DE-CAPITAL</t>
+          <t>https://www.apucarana.pr.gov.br/atrativos-da-serra/</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4500,11 +4500,11 @@
         <v>404</v>
       </c>
       <c r="E146" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-07-31 01:46:46</t>
+          <t>2026-08-03 10:21:21</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Pagina/POLITICA-DE-RESPONSABILIDADE-SOCIOAMBIENTAL</t>
+          <t>https://www.apucarana.pr.gov.br/atrativos-da-serra/</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4528,11 +4528,11 @@
         <v>404</v>
       </c>
       <c r="E147" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-07-31 01:46:53</t>
+          <t>2026-08-03 10:21:26</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Microcredito-Facil</t>
+          <t>https://www.apucarana.pr.gov.br/noites-em-apucarana/</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4556,11 +4556,11 @@
         <v>404</v>
       </c>
       <c r="E148" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-07-31 01:47:00</t>
+          <t>2026-08-03 10:21:26</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Banco-da-Mulher-Paranaense/Microcredito</t>
+          <t>https://www.apucarana.pr.gov.br/noites-em-apucarana/</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4584,11 +4584,11 @@
         <v>404</v>
       </c>
       <c r="E149" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-07-31 01:47:07</t>
+          <t>2026-08-03 10:21:36</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Credito/Banco-da-Mulher-Paranaense/MPE</t>
+          <t>https://www.apucarana.pr.gov.br/cafes-e-padarias/</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4612,11 +4612,11 @@
         <v>404</v>
       </c>
       <c r="E150" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-07-31 01:47:15</t>
+          <t>2026-08-03 10:21:36</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Credito/BANCO-DO-EMPREENDEDOR</t>
+          <t>https://www.apucarana.pr.gov.br/cafes-e-padarias/</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4640,11 +4640,11 @@
         <v>404</v>
       </c>
       <c r="E151" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-07-31 01:47:22</t>
+          <t>2026-08-03 10:21:46</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Emprestimos</t>
+          <t>https://www.apucarana.pr.gov.br/natureza/</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4668,11 +4668,11 @@
         <v>404</v>
       </c>
       <c r="E152" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-07-31 01:47:29</t>
+          <t>2026-08-03 10:21:46</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Credito/AMPLIACAO-CONSTRUCAO-E-REFORMA</t>
+          <t>https://www.apucarana.pr.gov.br/natureza/</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4696,11 +4696,11 @@
         <v>404</v>
       </c>
       <c r="E153" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-07-31 01:47:36</t>
+          <t>2026-08-03 10:22:16</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Credito/MAQUINAS-E-EQUIPAMENTOS</t>
+          <t>https://www.apucarana.pr.gov.br/arte-cultura/</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4724,11 +4724,11 @@
         <v>404</v>
       </c>
       <c r="E154" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-07-31 01:47:43</t>
+          <t>2026-08-03 10:22:16</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Credito/VEICULOS</t>
+          <t>https://www.apucarana.pr.gov.br/arte-cultura/</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4752,11 +4752,11 @@
         <v>404</v>
       </c>
       <c r="E155" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-07-31 01:47:50</t>
+          <t>2026-08-03 10:22:35</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Credito/Energias-Renovaveis</t>
+          <t>https://www.apucarana.pr.gov.br/tour/catedral-nossa-senhora-de-lourdes/</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4780,11 +4780,11 @@
         <v>404</v>
       </c>
       <c r="E156" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-31 01:47:58</t>
+          <t>2026-08-03 10:22:36</t>
         </is>
       </c>
     </row>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Credito/Fomento-Inova</t>
+          <t>https://www.apucarana.pr.gov.br/tour/praca-rui-barbosa/</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4808,11 +4808,11 @@
         <v>404</v>
       </c>
       <c r="E157" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-07-31 01:48:05</t>
+          <t>2026-08-03 10:23:10</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Credito/Recursos-BNDES</t>
+          <t>https://www.apucarana.pr.gov.br/tour/parque-jaboti/</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4836,11 +4836,11 @@
         <v>404</v>
       </c>
       <c r="E158" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-07-31 01:48:12</t>
+          <t>2026-08-03 10:23:45</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Credito/FINANCIAMENTOS-AO-SETOR-PUBLICO</t>
+          <t>https://www.apucarana.pr.gov.br/tour/parque-jaboti/</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4864,11 +4864,11 @@
         <v>404</v>
       </c>
       <c r="E159" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-07-31 01:48:13</t>
+          <t>2026-08-03 10:23:53</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Transparencia/Tabela-de-Tarifas</t>
+          <t>https://www.apucarana.pr.gov.br/tour/espaco-das-feiras/</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4892,11 +4892,11 @@
         <v>404</v>
       </c>
       <c r="E160" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-07-31 01:48:20</t>
+          <t>2026-08-03 10:23:54</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Pagina/CUSTO-EFETIVO-TOTAL-CET</t>
+          <t>https://www.apucarana.pr.gov.br/tour/espaco-das-feiras/</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4920,11 +4920,11 @@
         <v>404</v>
       </c>
       <c r="E161" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-07-31 01:48:27</t>
+          <t>2026-08-03 10:24:00</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Parcerias/AGENDA-DE-CURSOS</t>
+          <t>https://www.apucarana.pr.gov.br/tour/parque-ecologico-da-raposa/</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4948,11 +4948,11 @@
         <v>404</v>
       </c>
       <c r="E162" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-07-31 01:48:34</t>
+          <t>2026-08-03 10:24:01</t>
         </is>
       </c>
     </row>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Parcerias/AGENTES-DE-CREDITO</t>
+          <t>https://www.apucarana.pr.gov.br/tour/praca-maua/</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4976,11 +4976,11 @@
         <v>404</v>
       </c>
       <c r="E163" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-07-31 01:48:42</t>
+          <t>2026-08-03 10:24:35</t>
         </is>
       </c>
     </row>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Parcerias/SEJA-UM-AGENTE-DE-CREDITO</t>
+          <t>https://www.apucarana.pr.gov.br/tour/praca-maua/</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5004,11 +5004,11 @@
         <v>404</v>
       </c>
       <c r="E164" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-07-31 01:48:49</t>
+          <t>2026-08-03 10:24:51</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Pagina/NOSSOS-CORRESPONDENTES</t>
+          <t>https://www.apucarana.pr.gov.br/tour/parque-da-redencao/</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5032,11 +5032,11 @@
         <v>404</v>
       </c>
       <c r="E165" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-07-31 01:48:58</t>
+          <t>2026-08-03 10:24:51</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Pagina/CORRESPONDENTES</t>
+          <t>https://www.apucarana.pr.gov.br/tour/jardim-japones/</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5060,11 +5060,11 @@
         <v>404</v>
       </c>
       <c r="E166" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-07-31 01:49:05</t>
+          <t>2026-08-03 10:25:26</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Pagina/COMO-SE-TORNAR-CORRESPONDENTE</t>
+          <t>https://www.apucarana.pr.gov.br/tour/jardim-japones/</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5088,11 +5088,11 @@
         <v>404</v>
       </c>
       <c r="E167" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-07-31 01:49:12</t>
+          <t>2026-08-03 10:25:31</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Pagina/Transparencia</t>
+          <t>https://www.apucarana.pr.gov.br/tour/praca-da-onca/</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5116,11 +5116,11 @@
         <v>404</v>
       </c>
       <c r="E168" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-07-31 01:49:20</t>
+          <t>2026-08-03 10:25:31</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Transparencia/CONCURSOS-PUBLICOS</t>
+          <t>https://www.apucarana.pr.gov.br/tour/praca-da-onca/</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5144,11 +5144,11 @@
         <v>404</v>
       </c>
       <c r="E169" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-07-31 01:49:27</t>
+          <t>2026-08-03 10:25:46</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Transparencia/Editais</t>
+          <t>https://www.apucarana.pr.gov.br/tour/bosque-municipal/</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5172,11 +5172,11 @@
         <v>404</v>
       </c>
       <c r="E170" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-07-31 01:49:34</t>
+          <t>2026-08-03 10:25:46</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Transparencia/DEMONSTRATIVOS-CONTABEIS-FOMENTO-PARANA</t>
+          <t>https://www.apucarana.pr.gov.br/tour/museu-do-cafe/</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5200,11 +5200,11 @@
         <v>404</v>
       </c>
       <c r="E171" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-07-31 01:49:41</t>
+          <t>2026-08-03 10:26:21</t>
         </is>
       </c>
     </row>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Fundos/DEMONSTRATIVOS-CONTABEIS-GESTAO-DE-FUNDOS</t>
+          <t>https://www.apucarana.pr.gov.br/tour/museu-do-cafe/</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5228,11 +5228,11 @@
         <v>404</v>
       </c>
       <c r="E172" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-07-31 01:49:48</t>
+          <t>2026-08-03 10:26:26</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/contatos</t>
+          <t>https://www.apucarana.pr.gov.br/tour/parque-ecologico-santo-expedito/</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5256,11 +5256,11 @@
         <v>404</v>
       </c>
       <c r="E173" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-07-31 01:49:55</t>
+          <t>2026-08-03 10:26:26</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-credito-para-micro-e-pequenas-empresas-JVN6AGoP</t>
+          <t>https://www.apucarana.pr.gov.br/compre-roupas-direto-do-fabricante/</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5284,11 +5284,11 @@
         <v>404</v>
       </c>
       <c r="E174" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-07-31 01:50:03</t>
+          <t>2026-08-03 10:27:00</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-financiamento-ao-Banco-da-Mulher-Paranaense-aPo4dBom</t>
+          <t>https://www.apucarana.pr.gov.br/compre-roupas-direto-do-fabricante/</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5312,11 +5312,11 @@
         <v>404</v>
       </c>
       <c r="E175" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-07-31 01:50:10</t>
+          <t>2026-08-03 10:27:10</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-microcredito-para-empreendedores-nQ3x0z32</t>
+          <t>https://www.apucarana.pr.gov.br/roteiro-da-fe/</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5340,11 +5340,11 @@
         <v>404</v>
       </c>
       <c r="E176" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-07-31 01:50:17</t>
+          <t>2026-08-03 10:27:10</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/servicos/Empresa/Cadin/Consultar-se-o-CPF-ou-o-CNPJ-esta-inscrito-no-Cadin-aPo4ZB3m</t>
+          <t>https://www.apucarana.pr.gov.br/roteiro-da-fe/</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5368,11 +5368,11 @@
         <v>404</v>
       </c>
       <c r="E177" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-07-31 01:50:24</t>
+          <t>2026-08-03 10:27:16</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/servicos/Mais-buscados/Certidoes/Emitir-Certidao-Negativa-Receita-Estadual-kZrX5gol</t>
+          <t>https://www.apucarana.pr.gov.br/roteiros-turisticos/</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5396,11 +5396,11 @@
         <v>404</v>
       </c>
       <c r="E178" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-07-31 01:50:31</t>
+          <t>2026-08-03 10:27:17</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/servicos/Seguranca/Atestados-e-Certidoes/Solicitar-Atestado-de-Cadastro-Negativo-vGr5V6o0</t>
+          <t>https://www.apucarana.pr.gov.br/roteiros-turisticos/</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5424,11 +5424,11 @@
         <v>404</v>
       </c>
       <c r="E179" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-07-31 01:50:38</t>
+          <t>2026-08-03 10:27:46</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/servicos/Servicos/Meio-Ambiente/Solicitar-licenciamento-ambiental-9OoqbNG0</t>
+          <t>https://www.apucarana.pr.gov.br/tour/monumento-a-biblia/</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5452,11 +5452,11 @@
         <v>404</v>
       </c>
       <c r="E180" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-07-31 01:50:46</t>
+          <t>2026-08-03 10:27:46</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/servicos/Receita-PR/Acesso-ao-portal/Acessar-o-Portal-Receita-PR-ybrz8JN4</t>
+          <t>https://www.apucarana.pr.gov.br/tour/monumento-a-biblia/</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5480,11 +5480,11 @@
         <v>404</v>
       </c>
       <c r="E181" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-07-31 01:50:53</t>
+          <t>2026-08-03 10:28:08</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/servicos/Administracao/Documentos/Cadastrar-se-no-PIA-6K3WwW3m</t>
+          <t>https://www.apucarana.pr.gov.br/tour/monumento-ao-bone/</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5508,11 +5508,11 @@
         <v>404</v>
       </c>
       <c r="E182" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-07-31 01:51:00</t>
+          <t>2026-08-03 10:28:09</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/servicos/Seguranca/Corpo-de-Bombeiros/Solicitar-analise-de-projeto-pelo-Corpo-de-Bombeiros-0GNAZ387</t>
+          <t>https://www.apucarana.pr.gov.br/tour/monumento-ao-bone/</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5536,11 +5536,11 @@
         <v>404</v>
       </c>
       <c r="E183" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-07-31 01:51:07</t>
+          <t>2026-08-03 10:28:13</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/servicos/Servicos/Municipios/Solicitar-financiamento-do-BRDE-kZrXMDol</t>
+          <t>https://www.apucarana.pr.gov.br/tour/centro-civico/</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5564,11 +5564,11 @@
         <v>404</v>
       </c>
       <c r="E184" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-07-31 01:51:14</t>
+          <t>2026-08-03 10:28:13</t>
         </is>
       </c>
     </row>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/servicos/Servicos/Licenciamento/Solicitar-licenciamento-do-Corpo-de-Bombeiros-MD3PPn36</t>
+          <t>https://www.apucarana.pr.gov.br/tour/centro-civico/</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5592,11 +5592,11 @@
         <v>404</v>
       </c>
       <c r="E185" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-07-31 01:51:21</t>
+          <t>2026-08-03 10:28:44</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Pagina/Ouvidoria</t>
+          <t>https://www.apucarana.pr.gov.br/tour/memorial-casa-de-portugal-e-praca-jose-lebre-dos-santos/</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5620,11 +5620,11 @@
         <v>404</v>
       </c>
       <c r="E186" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-07-31 01:51:29</t>
+          <t>2026-08-03 10:28:44</t>
         </is>
       </c>
     </row>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/apucarana/</t>
+          <t>https://www.apucarana.pr.gov.br/tour/memorial-casa-de-portugal-e-praca-jose-lebre-dos-santos/</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5648,11 +5648,11 @@
         <v>404</v>
       </c>
       <c r="E187" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-31 01:51:36</t>
+          <t>2026-08-03 10:29:03</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/o-que-fazer/</t>
+          <t>https://www.apucarana.pr.gov.br/tour/exposicao-iconografica-josefina-mariana-e-marelliana/</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5676,11 +5676,11 @@
         <v>404</v>
       </c>
       <c r="E188" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-07-31 01:51:43</t>
+          <t>2026-08-03 10:29:04</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/onde-comer/</t>
+          <t>https://www.apucarana.pr.gov.br/tour/praca-28-de-janeiro/</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5704,11 +5704,11 @@
         <v>404</v>
       </c>
       <c r="E189" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-07-31 01:51:50</t>
+          <t>2026-08-03 10:29:38</t>
         </is>
       </c>
     </row>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/onde-ficar/</t>
+          <t>https://www.apucarana.pr.gov.br/tour/parque-biguacu/</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5732,11 +5732,11 @@
         <v>404</v>
       </c>
       <c r="E190" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-07-31 01:51:57</t>
+          <t>2026-08-03 10:30:13</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/eventos/</t>
+          <t>https://www.apucarana.pr.gov.br/tour/parque-biguacu/</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5760,11 +5760,11 @@
         <v>404</v>
       </c>
       <c r="E191" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2026-07-31 01:52:05</t>
+          <t>2026-08-03 10:30:22</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/servicos/</t>
+          <t>https://www.apucarana.pr.gov.br/tour/museu-municipal-de-apucarana/</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5788,11 +5788,11 @@
         <v>404</v>
       </c>
       <c r="E192" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-07-31 01:52:12</t>
+          <t>2026-08-03 10:30:22</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/ao-vivo/</t>
+          <t>https://www.apucarana.pr.gov.br/tour/museu-municipal-de-apucarana/</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5816,11 +5816,11 @@
         <v>404</v>
       </c>
       <c r="E193" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-07-31 01:52:13</t>
+          <t>2026-08-03 10:30:42</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/travel-guide/conhecendo-apucarana</t>
+          <t>https://www.apucarana.pr.gov.br/credenciamento/</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5844,11 +5844,11 @@
         <v>404</v>
       </c>
       <c r="E194" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2026-07-31 01:52:14</t>
+          <t>2026-08-03 10:30:42</t>
         </is>
       </c>
     </row>
@@ -5860,7 +5860,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/atrativos-da-serra/</t>
+          <t>https://www.apucarana.pr.gov.br/credenciamento/</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5872,11 +5872,11 @@
         <v>404</v>
       </c>
       <c r="E195" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>2026-07-31 01:52:17</t>
+          <t>2026-08-03 10:31:12</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/noites-em-apucarana/</t>
+          <t>https://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/multi.php</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -5900,11 +5900,11 @@
         <v>404</v>
       </c>
       <c r="E196" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2026-07-31 01:52:24</t>
+          <t>2026-08-03 10:31:54</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/cafes-e-padarias/</t>
+          <t>https://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/multi.php</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -5928,11 +5928,11 @@
         <v>404</v>
       </c>
       <c r="E197" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-07-31 01:52:31</t>
+          <t>2026-08-03 10:32:05</t>
         </is>
       </c>
     </row>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/natureza/</t>
+          <t>https://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/medica.php</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5956,11 +5956,11 @@
         <v>404</v>
       </c>
       <c r="E198" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2026-07-31 01:52:38</t>
+          <t>2026-08-03 10:32:07</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/arte-cultura/</t>
+          <t>https://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/editais.php</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5984,11 +5984,11 @@
         <v>404</v>
       </c>
       <c r="E199" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-07-31 01:52:45</t>
+          <t>2026-08-03 10:32:42</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/tour/catedral-nossa-senhora-de-lourdes/</t>
+          <t>https://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/editais.php</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6012,11 +6012,11 @@
         <v>404</v>
       </c>
       <c r="E200" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-07-31 01:52:53</t>
+          <t>2026-08-03 10:32:48</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/tour/praca-rui-barbosa/</t>
+          <t>https://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/inscricoes.php</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6040,11 +6040,11 @@
         <v>404</v>
       </c>
       <c r="E201" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-07-31 01:53:00</t>
+          <t>2026-08-03 10:32:51</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/tour/parque-jaboti/</t>
+          <t>https://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/inscricoes.php</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6068,11 +6068,11 @@
         <v>404</v>
       </c>
       <c r="E202" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-07-31 01:53:07</t>
+          <t>2026-08-03 10:32:56</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/tour/espaco-das-feiras/</t>
+          <t>https://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/contato.php</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6096,11 +6096,11 @@
         <v>404</v>
       </c>
       <c r="E203" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-07-31 01:53:14</t>
+          <t>2026-08-03 10:33:08</t>
         </is>
       </c>
     </row>
@@ -6112,7 +6112,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/tour/parque-ecologico-da-raposa/</t>
+          <t>https://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/contato.php</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6124,11 +6124,11 @@
         <v>404</v>
       </c>
       <c r="E204" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-07-31 01:53:21</t>
+          <t>2026-08-03 10:33:25</t>
         </is>
       </c>
     </row>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/tour/praca-maua/</t>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/e-obituarios</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6152,11 +6152,11 @@
         <v>404</v>
       </c>
       <c r="E205" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-07-31 01:53:29</t>
+          <t>2026-08-03 10:33:26</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/tour/parque-da-redencao/</t>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/e-obituarios</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6180,11 +6180,11 @@
         <v>404</v>
       </c>
       <c r="E206" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-07-31 01:53:36</t>
+          <t>2026-08-03 10:33:44</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/tour/jardim-japones/</t>
+          <t>https://www.apucarana.pr.gov.br/autoatendimento/servicos/e-obituarios/detalhar/1</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6208,11 +6208,11 @@
         <v>404</v>
       </c>
       <c r="E207" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-07-31 01:53:43</t>
+          <t>2026-08-03 10:33:44</t>
         </is>
       </c>
     </row>
@@ -6224,23 +6224,23 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/tour/praca-da-onca/</t>
+          <t>http://portal.apucarana.pr.gov.br/pronimtb/index.asp?acao=1&amp;item=91&amp;visao=0</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E208" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-07-31 01:53:50</t>
+          <t>2026-08-03 11:53:49</t>
         </is>
       </c>
     </row>
@@ -6252,23 +6252,23 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/tour/bosque-municipal/</t>
+          <t>http://www.apucarana.pr.gov.br/site/servicos/regularizacao-do-rotativo/</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E209" t="n">
         <v>6</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-07-31 01:53:57</t>
+          <t>2026-08-03 12:13:31</t>
         </is>
       </c>
     </row>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/tour/museu-do-cafe/</t>
+          <t>http://www.apucarana.pr.gov.br/sitemap</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2026-07-31 01:54:04</t>
+          <t>2026-08-03 12:13:42</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/tour/parque-ecologico-santo-expedito/</t>
+          <t>http://www.apucarana.pr.gov.br/sitemap</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-07-31 01:54:12</t>
+          <t>2026-08-03 12:13:49</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/compre-roupas-direto-do-fabricante/</t>
+          <t>http://www.apucarana.pr.gov.br/Institucional/MISSAO-VISAO-DE-FUTURO-VALORES</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-07-31 01:54:19</t>
+          <t>2026-08-03 12:13:49</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/roteiro-da-fe/</t>
+          <t>http://www.apucarana.pr.gov.br/Institucional/MISSAO-VISAO-DE-FUTURO-VALORES</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-07-31 01:54:26</t>
+          <t>2026-08-03 12:13:56</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/roteiros-turisticos/</t>
+          <t>http://www.apucarana.pr.gov.br/Institucional/QUEM-SOMOS-E-O-QUE-FAZEMOS</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-07-31 01:54:29</t>
+          <t>2026-08-03 12:13:56</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/tour/monumento-a-biblia/</t>
+          <t>http://www.apucarana.pr.gov.br/Institucional/QUEM-SOMOS-E-O-QUE-FAZEMOS</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-07-31 01:54:36</t>
+          <t>2026-08-03 12:14:03</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/tour/monumento-ao-bone/</t>
+          <t>http://www.apucarana.pr.gov.br/Institucional/DIRETORIA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2026-07-31 01:54:37</t>
+          <t>2026-08-03 12:14:03</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/tour/centro-civico/</t>
+          <t>http://www.apucarana.pr.gov.br/Institucional/DIRETORIA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2026-07-31 01:54:40</t>
+          <t>2026-08-03 12:14:10</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/tour/memorial-casa-de-portugal-e-praca-jose-lebre-dos-santos/</t>
+          <t>http://www.apucarana.pr.gov.br/Pagina/estatuto_social</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6520,7 +6520,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-07-31 01:54:41</t>
+          <t>2026-08-03 12:14:10</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/tour/exposicao-iconografica-josefina-mariana-e-marelliana/</t>
+          <t>http://www.apucarana.pr.gov.br/Pagina/estatuto_social</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>2026-07-31 01:54:49</t>
+          <t>2026-08-03 12:14:17</t>
         </is>
       </c>
     </row>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/tour/praca-28-de-janeiro/</t>
+          <t>http://www.apucarana.pr.gov.br/Pagina/GOVERNANCA-CORPORATIVA</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>2026-07-31 01:54:56</t>
+          <t>2026-08-03 12:14:17</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/tour/parque-biguacu/</t>
+          <t>http://www.apucarana.pr.gov.br/Pagina/GOVERNANCA-CORPORATIVA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>2026-07-31 01:55:03</t>
+          <t>2026-08-03 12:14:24</t>
         </is>
       </c>
     </row>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/tour/museu-municipal-de-apucarana/</t>
+          <t>http://www.apucarana.pr.gov.br/Institucional/ATIVIDADES-DE-GESTAO</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2026-07-31 01:55:10</t>
+          <t>2026-08-03 12:14:24</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/credenciamento/</t>
+          <t>http://www.apucarana.pr.gov.br/Institucional/ATIVIDADES-DE-GESTAO</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2026-07-31 01:55:18</t>
+          <t>2026-08-03 12:14:31</t>
         </is>
       </c>
     </row>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/multi.php</t>
+          <t>http://www.apucarana.pr.gov.br/Institucional/GESTAO-DE-RISCOS-E-GERENCIAMENTO-DE-CAPITAL</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2026-07-31 01:56:08</t>
+          <t>2026-08-03 12:14:31</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/medica.php</t>
+          <t>http://www.apucarana.pr.gov.br/Institucional/GESTAO-DE-RISCOS-E-GERENCIAMENTO-DE-CAPITAL</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-07-31 01:56:16</t>
+          <t>2026-08-03 12:14:38</t>
         </is>
       </c>
     </row>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/editais.php</t>
+          <t>http://www.apucarana.pr.gov.br/Pagina/POLITICA-DE-RESPONSABILIDADE-SOCIOAMBIENTAL</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2026-07-31 01:56:23</t>
+          <t>2026-08-03 12:14:38</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6756,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/inscricoes.php</t>
+          <t>http://www.apucarana.pr.gov.br/Pagina/POLITICA-DE-RESPONSABILIDADE-SOCIOAMBIENTAL</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2026-07-31 01:56:29</t>
+          <t>2026-08-03 12:14:45</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/contato.php</t>
+          <t>http://www.apucarana.pr.gov.br/Microcredito-Facil</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>2026-07-31 01:56:35</t>
+          <t>2026-08-03 12:14:46</t>
         </is>
       </c>
     </row>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos/e-obituarios</t>
+          <t>http://www.apucarana.pr.gov.br/Microcredito-Facil</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>2026-07-31 01:56:40</t>
+          <t>2026-08-03 12:14:52</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos/e-obituarios/detalhar/1</t>
+          <t>http://www.apucarana.pr.gov.br/Banco-da-Mulher-Paranaense/Microcredito</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>2026-07-31 01:56:48</t>
+          <t>2026-08-03 12:14:53</t>
         </is>
       </c>
     </row>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/ame/calendario-2/)</t>
+          <t>http://www.apucarana.pr.gov.br/Banco-da-Mulher-Paranaense/Microcredito</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -6880,11 +6880,11 @@
         <v>404</v>
       </c>
       <c r="E231" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2026-07-31 02:15:15</t>
+          <t>2026-08-03 12:14:59</t>
         </is>
       </c>
     </row>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/index.php</t>
+          <t>http://www.apucarana.pr.gov.br/Credito/Banco-da-Mulher-Paranaense/MPE</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6908,11 +6908,11 @@
         <v>404</v>
       </c>
       <c r="E232" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-07-31 02:40:21</t>
+          <t>2026-08-03 12:15:00</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/multi.php</t>
+          <t>http://www.apucarana.pr.gov.br/Credito/Banco-da-Mulher-Paranaense/MPE</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6936,11 +6936,11 @@
         <v>404</v>
       </c>
       <c r="E233" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2026-07-31 02:40:29</t>
+          <t>2026-08-03 12:15:06</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/medica.php</t>
+          <t>http://www.apucarana.pr.gov.br/Credito/BANCO-DO-EMPREENDEDOR</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -6964,11 +6964,11 @@
         <v>404</v>
       </c>
       <c r="E234" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>2026-07-31 02:40:36</t>
+          <t>2026-08-03 12:15:07</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/editais.php</t>
+          <t>http://www.apucarana.pr.gov.br/Credito/BANCO-DO-EMPREENDEDOR</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -6992,11 +6992,11 @@
         <v>404</v>
       </c>
       <c r="E235" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>2026-07-31 02:40:43</t>
+          <t>2026-08-03 12:15:13</t>
         </is>
       </c>
     </row>
@@ -7008,7 +7008,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/inscricoes.php</t>
+          <t>http://www.apucarana.pr.gov.br/Emprestimos</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7020,11 +7020,11 @@
         <v>404</v>
       </c>
       <c r="E236" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>2026-07-31 02:40:50</t>
+          <t>2026-08-03 12:15:14</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/contato.php</t>
+          <t>http://www.apucarana.pr.gov.br/Emprestimos</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7048,11 +7048,11 @@
         <v>404</v>
       </c>
       <c r="E237" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>2026-07-31 02:40:57</t>
+          <t>2026-08-03 12:15:20</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/Transparencia/Editais</t>
+          <t>http://www.apucarana.pr.gov.br/Credito/AMPLIACAO-CONSTRUCAO-E-REFORMA</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -7076,11 +7076,11 @@
         <v>404</v>
       </c>
       <c r="E238" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2026-07-31 02:44:31</t>
+          <t>2026-08-03 12:15:21</t>
         </is>
       </c>
     </row>
@@ -7092,7 +7092,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>https://www.apucarana.pr.gov.br/tour/jardim-japones/</t>
+          <t>http://www.apucarana.pr.gov.br/Credito/AMPLIACAO-CONSTRUCAO-E-REFORMA</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7104,11 +7104,11 @@
         <v>404</v>
       </c>
       <c r="E239" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-07-31 02:44:38</t>
+          <t>2026-08-03 12:15:27</t>
         </is>
       </c>
     </row>
@@ -7120,23 +7120,23 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>http://portal.apucarana.pr.gov.br/pronimtb/index.asp?acao=1&amp;item=91&amp;visao=0</t>
+          <t>http://www.apucarana.pr.gov.br/Credito/MAQUINAS-E-EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E240" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>2026-07-31 02:46:27</t>
+          <t>2026-08-03 12:15:28</t>
         </is>
       </c>
     </row>
@@ -7148,23 +7148,23 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>http://portal.apucarana.pr.gov.br/pronimtb/index.asp?acao=1&amp;item=91&amp;visao=0</t>
+          <t>http://www.apucarana.pr.gov.br/Credito/MAQUINAS-E-EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E241" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>2026-07-31 02:48:28</t>
+          <t>2026-08-03 12:15:34</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/autoatendimento/servicos/guias-de-iptu</t>
+          <t>http://www.apucarana.pr.gov.br/Credito/VEICULOS</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>2026-07-31 02:50:12</t>
+          <t>2026-08-03 12:15:35</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/sitemap</t>
+          <t>http://www.apucarana.pr.gov.br/Credito/VEICULOS</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>2026-07-31 02:50:19</t>
+          <t>2026-08-03 12:15:41</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Institucional/MISSAO-VISAO-DE-FUTURO-VALORES</t>
+          <t>http://www.apucarana.pr.gov.br/Credito/Energias-Renovaveis</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>2026-07-31 02:50:27</t>
+          <t>2026-08-03 12:15:42</t>
         </is>
       </c>
     </row>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/Credito/Recursos-BNDES</t>
+          <t>http://www.apucarana.pr.gov.br/Credito/Energias-Renovaveis</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>2026-07-31 02:50:34</t>
+          <t>2026-08-03 12:15:48</t>
         </is>
       </c>
     </row>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/servicos/</t>
+          <t>http://www.apucarana.pr.gov.br/Credito/Fomento-Inova</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>2026-07-31 02:50:41</t>
+          <t>2026-08-03 12:15:49</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/ao-vivo/</t>
+          <t>http://www.apucarana.pr.gov.br/Credito/Fomento-Inova</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>2026-07-31 02:50:48</t>
+          <t>2026-08-03 12:15:55</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/travel-guide/conhecendo-apucarana</t>
+          <t>http://www.apucarana.pr.gov.br/Credito/Recursos-BNDES</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>2026-07-31 02:50:55</t>
+          <t>2026-08-03 12:15:56</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/roteiro-da-fe/</t>
+          <t>http://www.apucarana.pr.gov.br/Credito/Recursos-BNDES</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-31 02:51:02</t>
+          <t>2026-08-03 12:16:00</t>
         </is>
       </c>
     </row>
@@ -7400,7 +7400,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/tour/monumento-a-biblia/</t>
+          <t>http://www.apucarana.pr.gov.br/Credito/FINANCIAMENTOS-AO-SETOR-PUBLICO</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>2026-07-31 02:51:09</t>
+          <t>2026-08-03 12:16:00</t>
         </is>
       </c>
     </row>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/tour/monumento-ao-bone/</t>
+          <t>http://www.apucarana.pr.gov.br/Credito/FINANCIAMENTOS-AO-SETOR-PUBLICO</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>2026-07-31 02:51:16</t>
+          <t>2026-08-03 12:16:07</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>http://www.apucarana.pr.gov.br/tour/centro-civico/</t>
+          <t>http://www.apucarana.pr.gov.br/Transparencia/Tabela-de-Tarifas</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>2026-07-31 02:51:23</t>
+          <t>2026-08-03 12:16:08</t>
         </is>
       </c>
     </row>
@@ -7484,23 +7484,23 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>https://apucarana.atende.net/transparencia/grupo/contas-publicas?agg=eyJncnVwbyI6IjEiLCJpZCI6IjlfMSJ9</t>
+          <t>http://www.apucarana.pr.gov.br/Transparencia/Tabela-de-Tarifas</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: SessionNotCreatedException</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E253" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>2026-07-31 03:45:24</t>
+          <t>2026-08-03 12:16:14</t>
         </is>
       </c>
     </row>
@@ -7512,23 +7512,23 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://apucarana.atende.net/transparencia/grupo/contas-publicas?agg=eyJncnVwbyI6IjEiLCJpZCI6IjdfMSJ9</t>
+          <t>http://www.apucarana.pr.gov.br/Pagina/CUSTO-EFETIVO-TOTAL-CET</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: SessionNotCreatedException</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E254" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>2026-07-31 03:45:25</t>
+          <t>2026-08-03 12:16:15</t>
         </is>
       </c>
     </row>
@@ -7540,23 +7540,4307 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>https://apucarana.atende.net/?pg=rest&amp;service=WNERestServiceNFSe</t>
+          <t>http://www.apucarana.pr.gov.br/Pagina/CUSTO-EFETIVO-TOTAL-CET</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>HTTP_401</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E255" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>2026-07-31 04:14:46</t>
+          <t>2026-08-03 12:16:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Parcerias/AGENDA-DE-CURSOS</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>404</v>
+      </c>
+      <c r="E256" t="n">
+        <v>6</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:16:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Parcerias/AGENDA-DE-CURSOS</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>404</v>
+      </c>
+      <c r="E257" t="n">
+        <v>6</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:16:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Parcerias/AGENTES-DE-CREDITO</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>404</v>
+      </c>
+      <c r="E258" t="n">
+        <v>6</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:16:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Parcerias/AGENTES-DE-CREDITO</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>404</v>
+      </c>
+      <c r="E259" t="n">
+        <v>6</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:16:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Parcerias/SEJA-UM-AGENTE-DE-CREDITO</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>404</v>
+      </c>
+      <c r="E260" t="n">
+        <v>6</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:16:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Parcerias/SEJA-UM-AGENTE-DE-CREDITO</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>404</v>
+      </c>
+      <c r="E261" t="n">
+        <v>6</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:16:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Pagina/NOSSOS-CORRESPONDENTES</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>404</v>
+      </c>
+      <c r="E262" t="n">
+        <v>6</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:16:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Pagina/NOSSOS-CORRESPONDENTES</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>404</v>
+      </c>
+      <c r="E263" t="n">
+        <v>6</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:16:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Pagina/CORRESPONDENTES</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>404</v>
+      </c>
+      <c r="E264" t="n">
+        <v>6</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:16:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Pagina/CORRESPONDENTES</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>404</v>
+      </c>
+      <c r="E265" t="n">
+        <v>6</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:16:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Pagina/COMO-SE-TORNAR-CORRESPONDENTE</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>404</v>
+      </c>
+      <c r="E266" t="n">
+        <v>6</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:16:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Pagina/COMO-SE-TORNAR-CORRESPONDENTE</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>404</v>
+      </c>
+      <c r="E267" t="n">
+        <v>6</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:17:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Pagina/Transparencia</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>404</v>
+      </c>
+      <c r="E268" t="n">
+        <v>6</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:17:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Pagina/Transparencia</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>404</v>
+      </c>
+      <c r="E269" t="n">
+        <v>6</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:17:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Transparencia/CONCURSOS-PUBLICOS</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>404</v>
+      </c>
+      <c r="E270" t="n">
+        <v>6</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:17:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Transparencia/CONCURSOS-PUBLICOS</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>404</v>
+      </c>
+      <c r="E271" t="n">
+        <v>6</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:17:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Transparencia/Editais</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>404</v>
+      </c>
+      <c r="E272" t="n">
+        <v>6</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:17:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Transparencia/Editais</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>404</v>
+      </c>
+      <c r="E273" t="n">
+        <v>6</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:17:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Transparencia/DEMONSTRATIVOS-CONTABEIS-FOMENTO-PARANA</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>404</v>
+      </c>
+      <c r="E274" t="n">
+        <v>6</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:17:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Transparencia/DEMONSTRATIVOS-CONTABEIS-FOMENTO-PARANA</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>404</v>
+      </c>
+      <c r="E275" t="n">
+        <v>6</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:17:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Fundos/DEMONSTRATIVOS-CONTABEIS-GESTAO-DE-FUNDOS</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>404</v>
+      </c>
+      <c r="E276" t="n">
+        <v>6</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:17:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Fundos/DEMONSTRATIVOS-CONTABEIS-GESTAO-DE-FUNDOS</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>404</v>
+      </c>
+      <c r="E277" t="n">
+        <v>6</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:17:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/contatos</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>404</v>
+      </c>
+      <c r="E278" t="n">
+        <v>6</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:17:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/contatos</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>404</v>
+      </c>
+      <c r="E279" t="n">
+        <v>6</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:17:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-credito-para-micro-e-pequenas-empresas-JVN6AGoP</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>404</v>
+      </c>
+      <c r="E280" t="n">
+        <v>6</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:17:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-credito-para-micro-e-pequenas-empresas-JVN6AGoP</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>404</v>
+      </c>
+      <c r="E281" t="n">
+        <v>6</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:17:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-financiamento-ao-Banco-da-Mulher-Paranaense-aPo4dBom</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>404</v>
+      </c>
+      <c r="E282" t="n">
+        <v>6</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:17:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-financiamento-ao-Banco-da-Mulher-Paranaense-aPo4dBom</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>404</v>
+      </c>
+      <c r="E283" t="n">
+        <v>6</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:17:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-microcredito-para-empreendedores-nQ3x0z32</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>404</v>
+      </c>
+      <c r="E284" t="n">
+        <v>6</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:17:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Fomento/Credito/Solicitar-microcredito-para-empreendedores-nQ3x0z32</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>404</v>
+      </c>
+      <c r="E285" t="n">
+        <v>6</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:18:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Empresa/Cadin/Consultar-se-o-CPF-ou-o-CNPJ-esta-inscrito-no-Cadin-aPo4ZB3m</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>404</v>
+      </c>
+      <c r="E286" t="n">
+        <v>6</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:18:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Empresa/Cadin/Consultar-se-o-CPF-ou-o-CNPJ-esta-inscrito-no-Cadin-aPo4ZB3m</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>404</v>
+      </c>
+      <c r="E287" t="n">
+        <v>6</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:18:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Mais-buscados/Certidoes/Emitir-Certidao-Negativa-Receita-Estadual-kZrX5gol</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>404</v>
+      </c>
+      <c r="E288" t="n">
+        <v>6</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:18:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Mais-buscados/Certidoes/Emitir-Certidao-Negativa-Receita-Estadual-kZrX5gol</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>404</v>
+      </c>
+      <c r="E289" t="n">
+        <v>6</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:18:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Seguranca/Atestados-e-Certidoes/Solicitar-Atestado-de-Cadastro-Negativo-vGr5V6o0</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>404</v>
+      </c>
+      <c r="E290" t="n">
+        <v>6</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:18:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Seguranca/Atestados-e-Certidoes/Solicitar-Atestado-de-Cadastro-Negativo-vGr5V6o0</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>404</v>
+      </c>
+      <c r="E291" t="n">
+        <v>6</v>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:18:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Servicos/Meio-Ambiente/Solicitar-licenciamento-ambiental-9OoqbNG0</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>404</v>
+      </c>
+      <c r="E292" t="n">
+        <v>6</v>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:18:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Servicos/Meio-Ambiente/Solicitar-licenciamento-ambiental-9OoqbNG0</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>404</v>
+      </c>
+      <c r="E293" t="n">
+        <v>6</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:18:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Receita-PR/Acesso-ao-portal/Acessar-o-Portal-Receita-PR-ybrz8JN4</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>404</v>
+      </c>
+      <c r="E294" t="n">
+        <v>6</v>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:18:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Receita-PR/Acesso-ao-portal/Acessar-o-Portal-Receita-PR-ybrz8JN4</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>404</v>
+      </c>
+      <c r="E295" t="n">
+        <v>6</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:18:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Administracao/Documentos/Cadastrar-se-no-PIA-6K3WwW3m</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>404</v>
+      </c>
+      <c r="E296" t="n">
+        <v>6</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:18:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Administracao/Documentos/Cadastrar-se-no-PIA-6K3WwW3m</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D297" t="n">
+        <v>404</v>
+      </c>
+      <c r="E297" t="n">
+        <v>6</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:18:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Seguranca/Corpo-de-Bombeiros/Solicitar-analise-de-projeto-pelo-Corpo-de-Bombeiros-0GNAZ387</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>404</v>
+      </c>
+      <c r="E298" t="n">
+        <v>6</v>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:18:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Seguranca/Corpo-de-Bombeiros/Solicitar-analise-de-projeto-pelo-Corpo-de-Bombeiros-0GNAZ387</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>404</v>
+      </c>
+      <c r="E299" t="n">
+        <v>6</v>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:18:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Servicos/Municipios/Solicitar-financiamento-do-BRDE-kZrXMDol</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>404</v>
+      </c>
+      <c r="E300" t="n">
+        <v>6</v>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:18:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Servicos/Municipios/Solicitar-financiamento-do-BRDE-kZrXMDol</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>404</v>
+      </c>
+      <c r="E301" t="n">
+        <v>6</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Servicos/Licenciamento/Solicitar-licenciamento-do-Corpo-de-Bombeiros-MD3PPn36</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>404</v>
+      </c>
+      <c r="E302" t="n">
+        <v>6</v>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/Servicos/Licenciamento/Solicitar-licenciamento-do-Corpo-de-Bombeiros-MD3PPn36</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>404</v>
+      </c>
+      <c r="E303" t="n">
+        <v>6</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:19:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Pagina/Ouvidoria</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>404</v>
+      </c>
+      <c r="E304" t="n">
+        <v>6</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:19:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/Pagina/Ouvidoria</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>404</v>
+      </c>
+      <c r="E305" t="n">
+        <v>6</v>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:19:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/apucarana/</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>404</v>
+      </c>
+      <c r="E306" t="n">
+        <v>6</v>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:19:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/apucarana/</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>404</v>
+      </c>
+      <c r="E307" t="n">
+        <v>6</v>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:19:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/o-que-fazer/</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D308" t="n">
+        <v>404</v>
+      </c>
+      <c r="E308" t="n">
+        <v>6</v>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:19:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/o-que-fazer/</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D309" t="n">
+        <v>404</v>
+      </c>
+      <c r="E309" t="n">
+        <v>6</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:19:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/onde-comer/</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>404</v>
+      </c>
+      <c r="E310" t="n">
+        <v>6</v>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:19:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/onde-comer/</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>404</v>
+      </c>
+      <c r="E311" t="n">
+        <v>6</v>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/onde-ficar/</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>404</v>
+      </c>
+      <c r="E312" t="n">
+        <v>6</v>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/onde-ficar/</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>404</v>
+      </c>
+      <c r="E313" t="n">
+        <v>6</v>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:19:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/eventos/</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>404</v>
+      </c>
+      <c r="E314" t="n">
+        <v>6</v>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:19:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/eventos/</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>404</v>
+      </c>
+      <c r="E315" t="n">
+        <v>6</v>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:19:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>404</v>
+      </c>
+      <c r="E316" t="n">
+        <v>6</v>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:19:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/servicos/</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>404</v>
+      </c>
+      <c r="E317" t="n">
+        <v>6</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:19:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/ao-vivo/</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>404</v>
+      </c>
+      <c r="E318" t="n">
+        <v>6</v>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:19:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/ao-vivo/</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>404</v>
+      </c>
+      <c r="E319" t="n">
+        <v>6</v>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:20:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/travel-guide/conhecendo-apucarana</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>404</v>
+      </c>
+      <c r="E320" t="n">
+        <v>6</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:20:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/travel-guide/conhecendo-apucarana</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>404</v>
+      </c>
+      <c r="E321" t="n">
+        <v>6</v>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/atrativos-da-serra/</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>404</v>
+      </c>
+      <c r="E322" t="n">
+        <v>6</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/atrativos-da-serra/</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>404</v>
+      </c>
+      <c r="E323" t="n">
+        <v>6</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:20:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/noites-em-apucarana/</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>404</v>
+      </c>
+      <c r="E324" t="n">
+        <v>6</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:20:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/noites-em-apucarana/</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>404</v>
+      </c>
+      <c r="E325" t="n">
+        <v>6</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:20:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/cafes-e-padarias/</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>404</v>
+      </c>
+      <c r="E326" t="n">
+        <v>6</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:20:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/cafes-e-padarias/</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>404</v>
+      </c>
+      <c r="E327" t="n">
+        <v>6</v>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:20:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/natureza/</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>404</v>
+      </c>
+      <c r="E328" t="n">
+        <v>6</v>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:20:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/natureza/</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>404</v>
+      </c>
+      <c r="E329" t="n">
+        <v>6</v>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:20:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/arte-cultura/</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>404</v>
+      </c>
+      <c r="E330" t="n">
+        <v>6</v>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:20:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/arte-cultura/</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>404</v>
+      </c>
+      <c r="E331" t="n">
+        <v>6</v>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:20:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/catedral-nossa-senhora-de-lourdes/</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>404</v>
+      </c>
+      <c r="E332" t="n">
+        <v>6</v>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:20:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/catedral-nossa-senhora-de-lourdes/</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>404</v>
+      </c>
+      <c r="E333" t="n">
+        <v>6</v>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:20:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/praca-rui-barbosa/</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>404</v>
+      </c>
+      <c r="E334" t="n">
+        <v>6</v>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:20:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/praca-rui-barbosa/</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D335" t="n">
+        <v>404</v>
+      </c>
+      <c r="E335" t="n">
+        <v>6</v>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:20:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/parque-jaboti/</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D336" t="n">
+        <v>404</v>
+      </c>
+      <c r="E336" t="n">
+        <v>6</v>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:20:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/parque-jaboti/</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D337" t="n">
+        <v>404</v>
+      </c>
+      <c r="E337" t="n">
+        <v>6</v>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/espaco-das-feiras/</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>404</v>
+      </c>
+      <c r="E338" t="n">
+        <v>6</v>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/espaco-das-feiras/</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D339" t="n">
+        <v>404</v>
+      </c>
+      <c r="E339" t="n">
+        <v>6</v>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/parque-ecologico-da-raposa/</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D340" t="n">
+        <v>404</v>
+      </c>
+      <c r="E340" t="n">
+        <v>6</v>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/parque-ecologico-da-raposa/</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D341" t="n">
+        <v>404</v>
+      </c>
+      <c r="E341" t="n">
+        <v>6</v>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/praca-maua/</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D342" t="n">
+        <v>404</v>
+      </c>
+      <c r="E342" t="n">
+        <v>6</v>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/praca-maua/</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D343" t="n">
+        <v>404</v>
+      </c>
+      <c r="E343" t="n">
+        <v>6</v>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/parque-da-redencao/</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D344" t="n">
+        <v>404</v>
+      </c>
+      <c r="E344" t="n">
+        <v>6</v>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/parque-da-redencao/</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D345" t="n">
+        <v>404</v>
+      </c>
+      <c r="E345" t="n">
+        <v>6</v>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/jardim-japones/</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D346" t="n">
+        <v>404</v>
+      </c>
+      <c r="E346" t="n">
+        <v>6</v>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/jardim-japones/</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D347" t="n">
+        <v>404</v>
+      </c>
+      <c r="E347" t="n">
+        <v>6</v>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/praca-da-onca/</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D348" t="n">
+        <v>404</v>
+      </c>
+      <c r="E348" t="n">
+        <v>6</v>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/praca-da-onca/</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D349" t="n">
+        <v>404</v>
+      </c>
+      <c r="E349" t="n">
+        <v>6</v>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/bosque-municipal/</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D350" t="n">
+        <v>404</v>
+      </c>
+      <c r="E350" t="n">
+        <v>6</v>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/bosque-municipal/</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D351" t="n">
+        <v>404</v>
+      </c>
+      <c r="E351" t="n">
+        <v>6</v>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/museu-do-cafe/</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D352" t="n">
+        <v>404</v>
+      </c>
+      <c r="E352" t="n">
+        <v>6</v>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/museu-do-cafe/</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D353" t="n">
+        <v>404</v>
+      </c>
+      <c r="E353" t="n">
+        <v>6</v>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/parque-ecologico-santo-expedito/</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D354" t="n">
+        <v>404</v>
+      </c>
+      <c r="E354" t="n">
+        <v>6</v>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:21:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/parque-ecologico-santo-expedito/</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D355" t="n">
+        <v>404</v>
+      </c>
+      <c r="E355" t="n">
+        <v>6</v>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:22:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/compre-roupas-direto-do-fabricante/</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D356" t="n">
+        <v>404</v>
+      </c>
+      <c r="E356" t="n">
+        <v>6</v>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:22:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/compre-roupas-direto-do-fabricante/</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D357" t="n">
+        <v>404</v>
+      </c>
+      <c r="E357" t="n">
+        <v>6</v>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:22:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/roteiro-da-fe/</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D358" t="n">
+        <v>404</v>
+      </c>
+      <c r="E358" t="n">
+        <v>6</v>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:22:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/roteiro-da-fe/</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D359" t="n">
+        <v>404</v>
+      </c>
+      <c r="E359" t="n">
+        <v>6</v>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:22:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/roteiros-turisticos/</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D360" t="n">
+        <v>404</v>
+      </c>
+      <c r="E360" t="n">
+        <v>6</v>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:22:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/roteiros-turisticos/</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D361" t="n">
+        <v>404</v>
+      </c>
+      <c r="E361" t="n">
+        <v>6</v>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:22:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/monumento-a-biblia/</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D362" t="n">
+        <v>404</v>
+      </c>
+      <c r="E362" t="n">
+        <v>6</v>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:22:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/monumento-a-biblia/</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D363" t="n">
+        <v>404</v>
+      </c>
+      <c r="E363" t="n">
+        <v>6</v>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:22:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/monumento-ao-bone/</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D364" t="n">
+        <v>404</v>
+      </c>
+      <c r="E364" t="n">
+        <v>6</v>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:22:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/monumento-ao-bone/</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D365" t="n">
+        <v>404</v>
+      </c>
+      <c r="E365" t="n">
+        <v>6</v>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:22:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/centro-civico/</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D366" t="n">
+        <v>404</v>
+      </c>
+      <c r="E366" t="n">
+        <v>6</v>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:22:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/centro-civico/</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D367" t="n">
+        <v>404</v>
+      </c>
+      <c r="E367" t="n">
+        <v>6</v>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:22:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/memorial-casa-de-portugal-e-praca-jose-lebre-dos-santos/</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D368" t="n">
+        <v>404</v>
+      </c>
+      <c r="E368" t="n">
+        <v>6</v>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:22:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/memorial-casa-de-portugal-e-praca-jose-lebre-dos-santos/</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D369" t="n">
+        <v>404</v>
+      </c>
+      <c r="E369" t="n">
+        <v>6</v>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:22:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/exposicao-iconografica-josefina-mariana-e-marelliana/</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D370" t="n">
+        <v>404</v>
+      </c>
+      <c r="E370" t="n">
+        <v>6</v>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:22:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/exposicao-iconografica-josefina-mariana-e-marelliana/</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D371" t="n">
+        <v>404</v>
+      </c>
+      <c r="E371" t="n">
+        <v>6</v>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:22:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/praca-28-de-janeiro/</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D372" t="n">
+        <v>404</v>
+      </c>
+      <c r="E372" t="n">
+        <v>6</v>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:22:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/praca-28-de-janeiro/</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D373" t="n">
+        <v>404</v>
+      </c>
+      <c r="E373" t="n">
+        <v>6</v>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:23:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/parque-biguacu/</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D374" t="n">
+        <v>404</v>
+      </c>
+      <c r="E374" t="n">
+        <v>6</v>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:23:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/parque-biguacu/</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D375" t="n">
+        <v>404</v>
+      </c>
+      <c r="E375" t="n">
+        <v>6</v>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:23:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/museu-municipal-de-apucarana/</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D376" t="n">
+        <v>404</v>
+      </c>
+      <c r="E376" t="n">
+        <v>6</v>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:23:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/tour/museu-municipal-de-apucarana/</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D377" t="n">
+        <v>404</v>
+      </c>
+      <c r="E377" t="n">
+        <v>6</v>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:23:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/credenciamento/</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D378" t="n">
+        <v>404</v>
+      </c>
+      <c r="E378" t="n">
+        <v>6</v>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:23:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/credenciamento/</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D379" t="n">
+        <v>404</v>
+      </c>
+      <c r="E379" t="n">
+        <v>6</v>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:23:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/multi.php</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D380" t="n">
+        <v>404</v>
+      </c>
+      <c r="E380" t="n">
+        <v>6</v>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:24:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/multi.php</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D381" t="n">
+        <v>404</v>
+      </c>
+      <c r="E381" t="n">
+        <v>6</v>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:24:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/medica.php</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D382" t="n">
+        <v>404</v>
+      </c>
+      <c r="E382" t="n">
+        <v>6</v>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:24:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/medica.php</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D383" t="n">
+        <v>404</v>
+      </c>
+      <c r="E383" t="n">
+        <v>6</v>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:24:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/editais.php</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D384" t="n">
+        <v>404</v>
+      </c>
+      <c r="E384" t="n">
+        <v>6</v>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:24:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/editais.php</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D385" t="n">
+        <v>404</v>
+      </c>
+      <c r="E385" t="n">
+        <v>6</v>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:24:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/inscricoes.php</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D386" t="n">
+        <v>404</v>
+      </c>
+      <c r="E386" t="n">
+        <v>6</v>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:24:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/inscricoes.php</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D387" t="n">
+        <v>404</v>
+      </c>
+      <c r="E387" t="n">
+        <v>6</v>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:25:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/contato.php</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D388" t="n">
+        <v>404</v>
+      </c>
+      <c r="E388" t="n">
+        <v>6</v>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:25:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/site/termos-de-busca/residencias-medicas/contato.php</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D389" t="n">
+        <v>404</v>
+      </c>
+      <c r="E389" t="n">
+        <v>6</v>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:25:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/ame/calendario-2/)</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D390" t="n">
+        <v>404</v>
+      </c>
+      <c r="E390" t="n">
+        <v>8</v>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:49:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/ame/calendario-2/)</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D391" t="n">
+        <v>404</v>
+      </c>
+      <c r="E391" t="n">
+        <v>8</v>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:50:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/index.php</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D392" t="n">
+        <v>404</v>
+      </c>
+      <c r="E392" t="n">
+        <v>10</v>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>2026-08-03 13:18:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/index.php</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D393" t="n">
+        <v>404</v>
+      </c>
+      <c r="E393" t="n">
+        <v>10</v>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>2026-08-03 13:18:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/multi.php</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D394" t="n">
+        <v>404</v>
+      </c>
+      <c r="E394" t="n">
+        <v>10</v>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>2026-08-03 13:18:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/multi.php</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D395" t="n">
+        <v>404</v>
+      </c>
+      <c r="E395" t="n">
+        <v>10</v>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>2026-08-03 13:19:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/medica.php</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D396" t="n">
+        <v>404</v>
+      </c>
+      <c r="E396" t="n">
+        <v>10</v>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>2026-08-03 13:19:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/medica.php</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D397" t="n">
+        <v>404</v>
+      </c>
+      <c r="E397" t="n">
+        <v>10</v>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>2026-08-03 13:19:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/editais.php</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D398" t="n">
+        <v>404</v>
+      </c>
+      <c r="E398" t="n">
+        <v>10</v>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>2026-08-03 13:19:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/editais.php</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D399" t="n">
+        <v>404</v>
+      </c>
+      <c r="E399" t="n">
+        <v>10</v>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>2026-08-03 13:19:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/inscricoes.php</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D400" t="n">
+        <v>404</v>
+      </c>
+      <c r="E400" t="n">
+        <v>10</v>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>2026-08-03 13:19:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/inscricoes.php</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D401" t="n">
+        <v>404</v>
+      </c>
+      <c r="E401" t="n">
+        <v>10</v>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>2026-08-03 13:19:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/contato.php</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D402" t="n">
+        <v>404</v>
+      </c>
+      <c r="E402" t="n">
+        <v>10</v>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>2026-08-03 13:19:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>http://www.apucarana.pr.gov.br/contato.php</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D403" t="n">
+        <v>404</v>
+      </c>
+      <c r="E403" t="n">
+        <v>10</v>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>2026-08-03 13:19:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>http://sys.apucarana.pr.gov.br/apucarana-pr/uploads/madspot_1433631749.php</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D404" t="n">
+        <v>404</v>
+      </c>
+      <c r="E404" t="n">
+        <v>3</v>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>2026-08-03 13:24:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>http://sys.apucarana.pr.gov.br/apucarana-pr/uploads/madspot_1433631749.php</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D405" t="n">
+        <v>0</v>
+      </c>
+      <c r="E405" t="n">
+        <v>3</v>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>2026-08-03 13:26:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>http://sys.apucarana.pr.gov.br/apucarana-pr/protocolo_fw/controle/protocolo_web_login.php</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D406" t="n">
+        <v>0</v>
+      </c>
+      <c r="E406" t="n">
+        <v>5</v>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>2026-08-03 13:29:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>http://portal.apucarana.pr.gov.br/pronimtb/index.asp?acao=1&amp;item=91&amp;visao=0</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D407" t="n">
+        <v>0</v>
+      </c>
+      <c r="E407" t="n">
+        <v>5</v>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>2026-08-03 13:32:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>apucarana</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>http://portal.apucarana.pr.gov.br/pronimtb/index.asp?acao=1&amp;item=91&amp;visao=0</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D408" t="n">
+        <v>0</v>
+      </c>
+      <c r="E408" t="n">
+        <v>5</v>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>2026-08-03 13:34:02</t>
         </is>
       </c>
     </row>
